--- a/Statistical_documentation_in_R/Control_group_construction/Replication_in_excel/solver_check_database_batch_3.xlsx
+++ b/Statistical_documentation_in_R/Control_group_construction/Replication_in_excel/solver_check_database_batch_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stoycho.rusinov\Documents\GitHub\Estimating_price_elasticity\Statistical_documentation_in_R\Control_group_construction\Checks_in_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stoycho/Documents/GitHub/Estimating_price_elasticity/Statistical_documentation_in_R/Control_group_construction/Replication_in_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6A63EC-A0A2-44B3-A8D8-0EEAC1B193E9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DFAD05-81C6-6F41-8FCF-209FADE8CE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="12" windowWidth="16092" windowHeight="9660" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="28480" windowHeight="15960" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="logmat" sheetId="1" r:id="rId1"/>
@@ -114,6 +114,19 @@
     <definedName name="solver_ver" localSheetId="4" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -824,7 +837,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -856,10 +869,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -890,21 +899,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -928,7 +937,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -956,7 +964,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -965,22 +973,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -992,12 +999,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1062,9 +1068,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1102,9 +1108,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1137,26 +1143,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1189,26 +1178,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1383,12 +1355,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H79"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1414,7 +1386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1440,7 +1412,7 @@
         <v>6.39024066706535</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1466,7 +1438,7 @@
         <v>6.3117348091529148</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1492,7 +1464,7 @@
         <v>5.0172798368149243</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1518,7 +1490,7 @@
         <v>6.0776422433490342</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1544,7 +1516,7 @@
         <v>6.0544393462693709</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1570,7 +1542,7 @@
         <v>6.9334230257307148</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1596,7 +1568,7 @@
         <v>5.1416635565026603</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1622,7 +1594,7 @@
         <v>5.8318824772835169</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1648,7 +1620,7 @@
         <v>5.8607862234658654</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1674,7 +1646,7 @@
         <v>7.568379267836522</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1700,7 +1672,7 @@
         <v>7.8481530861995257</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1726,7 +1698,7 @@
         <v>10.190769544966569</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1752,7 +1724,7 @@
         <v>5.8749307308520304</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1778,7 +1750,7 @@
         <v>7.8845765105963244</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1804,7 +1776,7 @@
         <v>7.1861443045223252</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1830,7 +1802,7 @@
         <v>6.1548580940164177</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1856,7 +1828,7 @@
         <v>6.7867169506050811</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1882,7 +1854,7 @@
         <v>5.9939614273065693</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -1908,7 +1880,7 @@
         <v>6.5944134597497781</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1934,7 +1906,7 @@
         <v>8.5794165345963691</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -1960,7 +1932,7 @@
         <v>8.0867179203039061</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -1986,7 +1958,7 @@
         <v>6.1862086239004936</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -2012,7 +1984,7 @@
         <v>7.7689560445383323</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -2038,7 +2010,7 @@
         <v>7.0039741367226798</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -2064,7 +2036,7 @@
         <v>9.1045353130792055</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -2090,7 +2062,7 @@
         <v>6.7044143549641069</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -2116,7 +2088,7 @@
         <v>5.7397929121792339</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -2142,7 +2114,7 @@
         <v>8.3816025371098899</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -2168,7 +2140,7 @@
         <v>4.9836066217083363</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -2194,7 +2166,7 @@
         <v>8.3311045480530392</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -2220,7 +2192,7 @@
         <v>6.4785096422085688</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -2246,7 +2218,7 @@
         <v>6.2653012127377101</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -2272,7 +2244,7 @@
         <v>5.7714411231300158</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>41</v>
       </c>
@@ -2298,7 +2270,7 @@
         <v>6.6147256002037604</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>42</v>
       </c>
@@ -2324,7 +2296,7 @@
         <v>7.4271441334086159</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>43</v>
       </c>
@@ -2350,7 +2322,7 @@
         <v>7.0698741284585722</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -2376,7 +2348,7 @@
         <v>6.4937538398516859</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>45</v>
       </c>
@@ -2402,7 +2374,7 @@
         <v>6.3733197895770122</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -2428,7 +2400,7 @@
         <v>7.4650827363995473</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -2454,7 +2426,7 @@
         <v>6.0306852602612633</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -2480,7 +2452,7 @@
         <v>8.2967958657700525</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>49</v>
       </c>
@@ -2506,7 +2478,7 @@
         <v>4.9126548857360524</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>50</v>
       </c>
@@ -2532,7 +2504,7 @@
         <v>5.8171111599632042</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>51</v>
       </c>
@@ -2558,7 +2530,7 @@
         <v>5.5451774444795623</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>52</v>
       </c>
@@ -2584,7 +2556,7 @@
         <v>6.1114673395026786</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>53</v>
       </c>
@@ -2610,7 +2582,7 @@
         <v>6.8362592772770672</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -2636,7 +2608,7 @@
         <v>5.1704839950381514</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -2662,7 +2634,7 @@
         <v>7.7367436824534952</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -2688,7 +2660,7 @@
         <v>7.2626286009742413</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -2714,7 +2686,7 @@
         <v>6.0661080901037474</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -2740,7 +2712,7 @@
         <v>7.8539930872242438</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -2766,7 +2738,7 @@
         <v>5.3752784076841653</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>60</v>
       </c>
@@ -2792,7 +2764,7 @@
         <v>8.4889994570454554</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -2818,7 +2790,7 @@
         <v>7.8674885686991276</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>62</v>
       </c>
@@ -2844,7 +2816,7 @@
         <v>6.4630294569206699</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>63</v>
       </c>
@@ -2870,7 +2842,7 @@
         <v>8.2271082343481456</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -2896,7 +2868,7 @@
         <v>6.7226297948554494</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>65</v>
       </c>
@@ -2922,7 +2894,7 @@
         <v>7.2765564027187102</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -2948,7 +2920,7 @@
         <v>8.1958853913147962</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -2974,7 +2946,7 @@
         <v>6.9431224228194282</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>68</v>
       </c>
@@ -3000,7 +2972,7 @@
         <v>4.836281906951478</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -3026,7 +2998,7 @@
         <v>6.6012301187288767</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>70</v>
       </c>
@@ -3052,7 +3024,7 @@
         <v>8.4383664108702661</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>71</v>
       </c>
@@ -3078,7 +3050,7 @@
         <v>5.9687075599853658</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>72</v>
       </c>
@@ -3104,7 +3076,7 @@
         <v>7.0783415795576712</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>73</v>
       </c>
@@ -3130,7 +3102,7 @@
         <v>7.2591161280971006</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>74</v>
       </c>
@@ -3156,7 +3128,7 @@
         <v>6.39024066706535</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>75</v>
       </c>
@@ -3182,7 +3154,7 @@
         <v>4.9836066217083363</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>76</v>
       </c>
@@ -3208,7 +3180,7 @@
         <v>6.9087547793152204</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>77</v>
       </c>
@@ -3234,7 +3206,7 @@
         <v>5.1704839950381514</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>78</v>
       </c>
@@ -3260,7 +3232,7 @@
         <v>7.2269360184932889</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>79</v>
       </c>
@@ -3286,7 +3258,7 @@
         <v>5.4424177105217932</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>80</v>
       </c>
@@ -3312,7 +3284,7 @@
         <v>5.5254529391317826</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>81</v>
       </c>
@@ -3338,7 +3310,7 @@
         <v>7.9483852851118986</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>82</v>
       </c>
@@ -3364,7 +3336,7 @@
         <v>8.5747070976168445</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -3390,7 +3362,7 @@
         <v>6.1964441277945204</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>84</v>
       </c>
@@ -3416,7 +3388,7 @@
         <v>5.0814043649844631</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>85</v>
       </c>
@@ -3453,12 +3425,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D79"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" customWidth="1"/>
+    <col min="1" max="1" width="21.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
@@ -3472,7 +3444,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3486,7 +3458,7 @@
         <v>1.5201323986969979</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3500,7 +3472,7 @@
         <v>1.96758071605122</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3514,7 +3486,7 @@
         <v>2.5917943242179331</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -3528,7 +3500,7 @@
         <v>1.454306935496537</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -3542,7 +3514,7 @@
         <v>2.2261430818371331</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -3556,7 +3528,7 @@
         <v>2.7219149317755011</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>17</v>
       </c>
@@ -3570,7 +3542,7 @@
         <v>1.917850942661258</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>17</v>
       </c>
@@ -3584,7 +3556,7 @@
         <v>2.0880670236391929</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>17</v>
       </c>
@@ -3598,7 +3570,7 @@
         <v>2.1317474833802672</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3612,7 +3584,7 @@
         <v>0.78556761100698713</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -3626,7 +3598,7 @@
         <v>0.91899781770672062</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -3640,49 +3612,49 @@
         <v>1.30529313006485</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="51" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="51">
+      <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14">
         <v>1.322443440920442</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="51" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="51">
+      <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15">
         <v>1.3264343933885541</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="51" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="51">
+      <c r="B16">
         <v>3</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16">
         <v>1.5522362059721759</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>22</v>
       </c>
@@ -3696,7 +3668,7 @@
         <v>0.71480107750477195</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>22</v>
       </c>
@@ -3710,7 +3682,7 @@
         <v>0.9325909975614225</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>22</v>
       </c>
@@ -3724,7 +3696,7 @@
         <v>1.051645326352604</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -3738,7 +3710,7 @@
         <v>1.313773130643523</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -3752,7 +3724,7 @@
         <v>2.120359351148926</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -3766,7 +3738,7 @@
         <v>2.232442595052639</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>25</v>
       </c>
@@ -3780,7 +3752,7 @@
         <v>0.40515867686517359</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
@@ -3794,7 +3766,7 @@
         <v>0.64096277571583637</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
@@ -3808,7 +3780,7 @@
         <v>0.83151090125850191</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
@@ -3822,7 +3794,7 @@
         <v>1.3533316400776481</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>26</v>
       </c>
@@ -3836,7 +3808,7 @@
         <v>1.474876419808983</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>26</v>
       </c>
@@ -3850,7 +3822,7 @@
         <v>1.800031410273109</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -3864,7 +3836,7 @@
         <v>0.92160942195897999</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -3878,7 +3850,7 @@
         <v>1.189670822588075</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -3892,7 +3864,7 @@
         <v>1.3889132086567619</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -3906,7 +3878,7 @@
         <v>1.7033345140888809</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -3920,7 +3892,7 @@
         <v>1.7918969996678871</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -3934,7 +3906,7 @@
         <v>2.3017385620529969</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>30</v>
       </c>
@@ -3948,7 +3920,7 @@
         <v>1.2009918077028521</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>30</v>
       </c>
@@ -3962,7 +3934,7 @@
         <v>1.7103959306010279</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -3976,7 +3948,7 @@
         <v>1.808807969188861</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>31</v>
       </c>
@@ -3990,7 +3962,7 @@
         <v>0.79318871004131175</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>31</v>
       </c>
@@ -4004,7 +3976,7 @@
         <v>0.85185327995696714</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>31</v>
       </c>
@@ -4018,7 +3990,7 @@
         <v>0.85626509773255732</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -4032,7 +4004,7 @@
         <v>1.598831204249944</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -4046,7 +4018,7 @@
         <v>2.2108702359853529</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>37</v>
       </c>
@@ -4060,7 +4032,7 @@
         <v>2.2214795218385919</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -4074,7 +4046,7 @@
         <v>0.89148389228016534</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -4088,7 +4060,7 @@
         <v>0.93305152918571599</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -4102,7 +4074,7 @@
         <v>1.0599816380974989</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -4116,7 +4088,7 @@
         <v>1.941244593289468</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -4130,7 +4102,7 @@
         <v>2.1131810226092602</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -4144,7 +4116,7 @@
         <v>2.7562972225803239</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>47</v>
       </c>
@@ -4158,7 +4130,7 @@
         <v>1.947053505032581</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>47</v>
       </c>
@@ -4172,7 +4144,7 @@
         <v>2.0948857998131589</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>47</v>
       </c>
@@ -4186,7 +4158,7 @@
         <v>2.1024054059528718</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>49</v>
       </c>
@@ -4200,7 +4172,7 @@
         <v>0.95290565026523966</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>49</v>
       </c>
@@ -4214,7 +4186,7 @@
         <v>1.1518565613407989</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -4228,7 +4200,7 @@
         <v>1.260223225287554</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -4242,7 +4214,7 @@
         <v>1.175180669759281</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>53</v>
       </c>
@@ -4256,7 +4228,7 @@
         <v>1.469126013073129</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>53</v>
       </c>
@@ -4270,7 +4242,7 @@
         <v>1.712976122044839</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -4284,7 +4256,7 @@
         <v>0.78940335234920489</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>60</v>
       </c>
@@ -4298,7 +4270,7 @@
         <v>0.81905046088821232</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -4312,7 +4284,7 @@
         <v>0.82781295435553304</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -4326,7 +4298,7 @@
         <v>0.45453412288402018</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -4340,7 +4312,7 @@
         <v>0.53020881439454659</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>61</v>
       </c>
@@ -4354,7 +4326,7 @@
         <v>0.60983050696296248</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -4368,7 +4340,7 @@
         <v>1.2982732123665801</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>63</v>
       </c>
@@ -4382,7 +4354,7 @@
         <v>1.5008085566896261</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>63</v>
       </c>
@@ -4396,7 +4368,7 @@
         <v>1.621690193249878</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -4410,7 +4382,7 @@
         <v>0.86344646830358396</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>67</v>
       </c>
@@ -4424,7 +4396,7 @@
         <v>1.0722629805507189</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>67</v>
       </c>
@@ -4438,7 +4410,7 @@
         <v>1.104413029623214</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>68</v>
       </c>
@@ -4452,7 +4424,7 @@
         <v>2.1291492212480332</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>68</v>
       </c>
@@ -4466,7 +4438,7 @@
         <v>2.1988526983046301</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>68</v>
       </c>
@@ -4480,7 +4452,7 @@
         <v>2.3318618917830038</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>70</v>
       </c>
@@ -4494,7 +4466,7 @@
         <v>0.70076211109565234</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>70</v>
       </c>
@@ -4508,7 +4480,7 @@
         <v>0.73680332091938594</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>70</v>
       </c>
@@ -4522,7 +4494,7 @@
         <v>0.75838741757894579</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>72</v>
       </c>
@@ -4536,7 +4508,7 @@
         <v>0.64602007029833564</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>72</v>
       </c>
@@ -4550,7 +4522,7 @@
         <v>0.79765965307815123</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>72</v>
       </c>
@@ -4572,877 +4544,877 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C79"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="16.33203125" style="65" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="61" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="65">
+      <c r="C2" s="62">
         <v>2.0363097138546361E-9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="65">
+      <c r="C3" s="62">
         <v>0.64903507398879612</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="65">
+      <c r="C4" s="62">
         <v>0.35096492397489409</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="65">
+      <c r="C5" s="62">
         <v>0.99999873825536978</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="65">
+      <c r="C6" s="62">
         <v>1.2517394440572831E-6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="65">
+      <c r="C7" s="62">
         <v>1.000518617098721E-8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="65">
+      <c r="C8" s="62">
         <v>0.67580221289686704</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="65">
+      <c r="C9" s="62">
         <v>0.32419778655420278</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="65">
+      <c r="C10" s="62">
         <v>5.4893011563366283E-10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
       <c r="B11" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="65">
+      <c r="C11" s="62">
         <v>1.123184115723512E-9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
       <c r="B12" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="65">
+      <c r="C12" s="62">
         <v>1.3048872302889341E-8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="65">
+      <c r="C13" s="62">
         <v>0.99999998582794369</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="65">
+      <c r="C14" s="62">
         <v>7.7418319723476075E-10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
       <c r="B15" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="65">
+      <c r="C15" s="62">
         <v>0.79471318156278947</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="65">
+      <c r="C16" s="62">
         <v>0.2052868176630272</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="65">
+      <c r="C17" s="62">
         <v>0.31777391101652008</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>22</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="65">
+      <c r="C18" s="62">
         <v>0.68222606641491146</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="65">
+      <c r="C19" s="62">
         <v>2.2568568492421111E-8</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="65">
+      <c r="C20" s="62">
         <v>0.45973532226379249</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>23</v>
       </c>
       <c r="B21" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="65">
+      <c r="C21" s="62">
         <v>8.0865157072275651E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="65">
+      <c r="C22" s="62">
         <v>0.45939952066393192</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="65">
+      <c r="C23" s="62">
         <v>1.5650705155873499E-9</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>25</v>
       </c>
       <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="65">
+      <c r="C24" s="62">
         <v>2.8177492279081748E-10</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
       <c r="B25" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="65">
+      <c r="C25" s="62">
         <v>0.99999999815315466</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
       <c r="B26" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="65">
+      <c r="C26" s="62">
         <v>2.7079212771711909E-11</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="65">
+      <c r="C27" s="62">
         <v>0.99999999832666442</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="65">
+      <c r="C28" s="62">
         <v>1.6462565278836949E-9</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="65">
+      <c r="C29" s="62">
         <v>0.99999992608228272</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>27</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="65">
+      <c r="C30" s="62">
         <v>1.3838223336319641E-9</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>27</v>
       </c>
       <c r="B31" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="65">
+      <c r="C31" s="62">
         <v>7.2533895014210998E-8</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="65">
+      <c r="C32" s="62">
         <v>1.7944391509783481E-6</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>28</v>
       </c>
       <c r="B33" t="s">
         <v>77</v>
       </c>
-      <c r="C33" s="65">
+      <c r="C33" s="62">
         <v>0.99999820536976203</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>28</v>
       </c>
       <c r="B34" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="65">
+      <c r="C34" s="62">
         <v>1.910871013607014E-10</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>30</v>
       </c>
       <c r="B35" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="65">
+      <c r="C35" s="62">
         <v>0.29239882456873839</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>30</v>
       </c>
       <c r="B36" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="65">
+      <c r="C36" s="62">
         <v>0.70760117535026024</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>30</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="65">
+      <c r="C37" s="62">
         <v>8.1001349514994056E-11</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>31</v>
       </c>
       <c r="B38" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="65">
+      <c r="C38" s="62">
         <v>0.2277946293803047</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>31</v>
       </c>
       <c r="B39" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="65">
+      <c r="C39" s="62">
         <v>0.59250011986721529</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>31</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="65">
+      <c r="C40" s="62">
         <v>0.17970525075248001</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>37</v>
       </c>
       <c r="B41" t="s">
         <v>77</v>
       </c>
-      <c r="C41" s="65">
+      <c r="C41" s="62">
         <v>0.99999846482277954</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>37</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="65">
+      <c r="C42" s="62">
         <v>4.1863649963411411E-10</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>37</v>
       </c>
       <c r="B43" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="65">
+      <c r="C43" s="62">
         <v>1.534758584483447E-6</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>44</v>
       </c>
       <c r="B44" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="65">
+      <c r="C44" s="62">
         <v>1.199532595512779E-12</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>44</v>
       </c>
       <c r="B45" t="s">
         <v>85</v>
       </c>
-      <c r="C45" s="65">
+      <c r="C45" s="62">
         <v>0.96067366971460844</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>44</v>
       </c>
       <c r="B46" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="65">
+      <c r="C46" s="62">
         <v>3.9326330284191947E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>46</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="65">
+      <c r="C47" s="62">
         <v>1.202984178023427E-10</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>46</v>
       </c>
       <c r="B48" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="65">
+      <c r="C48" s="62">
         <v>8.7987163081138333E-9</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>46</v>
       </c>
       <c r="B49" t="s">
         <v>62</v>
       </c>
-      <c r="C49" s="65">
+      <c r="C49" s="62">
         <v>0.99999999108098547</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>47</v>
       </c>
       <c r="B50" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="65">
+      <c r="C50" s="62">
         <v>0.24192905717418789</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>47</v>
       </c>
       <c r="B51" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="65">
+      <c r="C51" s="62">
         <v>0.32611526601641638</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>47</v>
       </c>
       <c r="B52" t="s">
         <v>75</v>
       </c>
-      <c r="C52" s="65">
+      <c r="C52" s="62">
         <v>0.43195567680939573</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>49</v>
       </c>
       <c r="B53" t="s">
         <v>51</v>
       </c>
-      <c r="C53" s="65">
+      <c r="C53" s="62">
         <v>1.7342610302663891E-7</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>49</v>
       </c>
       <c r="B54" t="s">
         <v>73</v>
       </c>
-      <c r="C54" s="65">
+      <c r="C54" s="62">
         <v>2.1726236488301869E-10</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>49</v>
       </c>
       <c r="B55" t="s">
         <v>36</v>
       </c>
-      <c r="C55" s="65">
+      <c r="C55" s="62">
         <v>0.99999982635663465</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>53</v>
       </c>
       <c r="B56" t="s">
         <v>42</v>
       </c>
-      <c r="C56" s="65">
+      <c r="C56" s="62">
         <v>0.39986170408838201</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>53</v>
       </c>
       <c r="B57" t="s">
         <v>24</v>
       </c>
-      <c r="C57" s="65">
+      <c r="C57" s="62">
         <v>0.1643168440569889</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>53</v>
       </c>
       <c r="B58" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="65">
+      <c r="C58" s="62">
         <v>0.43582145185462912</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>60</v>
       </c>
       <c r="B59" t="s">
         <v>42</v>
       </c>
-      <c r="C59" s="65">
+      <c r="C59" s="62">
         <v>0.9999998852556381</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>60</v>
       </c>
       <c r="B60" t="s">
         <v>79</v>
       </c>
-      <c r="C60" s="65">
+      <c r="C60" s="62">
         <v>3.3097314909353621E-10</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>60</v>
       </c>
       <c r="B61" t="s">
         <v>78</v>
       </c>
-      <c r="C61" s="65">
+      <c r="C61" s="62">
         <v>1.1441338874861271E-7</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>61</v>
       </c>
       <c r="B62" t="s">
         <v>33</v>
       </c>
-      <c r="C62" s="65">
+      <c r="C62" s="62">
         <v>7.6725612798815526E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>61</v>
       </c>
       <c r="B63" t="s">
         <v>82</v>
       </c>
-      <c r="C63" s="65">
+      <c r="C63" s="62">
         <v>1.687688923342771E-9</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>61</v>
       </c>
       <c r="B64" t="s">
         <v>81</v>
       </c>
-      <c r="C64" s="65">
+      <c r="C64" s="62">
         <v>0.92327438551349561</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>63</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
       </c>
-      <c r="C65" s="65">
+      <c r="C65" s="62">
         <v>2.7033091665574352E-13</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>63</v>
       </c>
       <c r="B66" t="s">
         <v>73</v>
       </c>
-      <c r="C66" s="65">
+      <c r="C66" s="62">
         <v>3.3301639146560272E-7</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>63</v>
       </c>
       <c r="B67" t="s">
         <v>42</v>
       </c>
-      <c r="C67" s="65">
+      <c r="C67" s="62">
         <v>0.9999996669833382</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>67</v>
       </c>
       <c r="B68" t="s">
         <v>51</v>
       </c>
-      <c r="C68" s="65">
+      <c r="C68" s="62">
         <v>0.61909911223363645</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>67</v>
       </c>
       <c r="B69" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="65">
+      <c r="C69" s="62">
         <v>0.29050540905599781</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>67</v>
       </c>
       <c r="B70" t="s">
         <v>45</v>
       </c>
-      <c r="C70" s="65">
+      <c r="C70" s="62">
         <v>9.039547871036574E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>68</v>
       </c>
       <c r="B71" t="s">
         <v>48</v>
       </c>
-      <c r="C71" s="65">
+      <c r="C71" s="62">
         <v>6.2071219128572069E-10</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>68</v>
       </c>
       <c r="B72" t="s">
         <v>64</v>
       </c>
-      <c r="C72" s="65">
+      <c r="C72" s="62">
         <v>7.5412267184569806E-8</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>68</v>
       </c>
       <c r="B73" t="s">
         <v>50</v>
       </c>
-      <c r="C73" s="65">
+      <c r="C73" s="62">
         <v>0.99999992396702087</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>70</v>
       </c>
       <c r="B74" t="s">
         <v>82</v>
       </c>
-      <c r="C74" s="65">
+      <c r="C74" s="62">
         <v>0.87392972297862725</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>70</v>
       </c>
       <c r="B75" t="s">
         <v>79</v>
       </c>
-      <c r="C75" s="65">
+      <c r="C75" s="62">
         <v>2.2439626276665712E-9</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>70</v>
       </c>
       <c r="B76" t="s">
         <v>33</v>
       </c>
-      <c r="C76" s="65">
+      <c r="C76" s="62">
         <v>0.1260702747774102</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>72</v>
       </c>
       <c r="B77" t="s">
         <v>48</v>
       </c>
-      <c r="C77" s="65">
+      <c r="C77" s="62">
         <v>4.1636069321933687E-9</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>72</v>
       </c>
       <c r="B78" t="s">
         <v>64</v>
       </c>
-      <c r="C78" s="65">
+      <c r="C78" s="62">
         <v>0.80290188916571481</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>72</v>
       </c>
       <c r="B79" t="s">
         <v>35</v>
       </c>
-      <c r="C79" s="65">
+      <c r="C79" s="62">
         <v>0.19709810667067831</v>
       </c>
     </row>
@@ -5457,45 +5429,42 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="B1:R41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" style="2" customWidth="1"/>
-    <col min="5" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="12.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.77734375" customWidth="1"/>
-    <col min="12" max="12" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
     <col min="13" max="18" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
+    <row r="1" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B2" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="18"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="76" t="s">
+      <c r="C2" s="14"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B3" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="19"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="20" t="s">
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="18" t="s">
         <v>86</v>
       </c>
       <c r="C4" s="9" t="s">
@@ -5507,13 +5476,10 @@
       <c r="E4" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="19"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="21" t="s">
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="19" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="11">
@@ -5525,13 +5491,10 @@
       <c r="E5" s="11">
         <v>1.917850942661258</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="19"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="21" t="s">
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="19" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="11">
@@ -5543,13 +5506,10 @@
       <c r="E6" s="11">
         <v>2.0880670236391929</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="21" t="s">
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="2:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="B7" s="19" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="11">
@@ -5561,35 +5521,26 @@
       <c r="E7" s="11">
         <v>2.1317474833802672</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="19"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="22"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="73" t="s">
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B8" s="20"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="75"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="23" t="s">
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="71"/>
+    </row>
+    <row r="10" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="21" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -5610,12 +5561,12 @@
       <c r="H10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="23" t="s">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B11" s="21" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="7">
@@ -5636,12 +5587,12 @@
       <c r="H11" s="7">
         <v>7.6596429545646822</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="22">
         <v>7.568379267836522</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="23" t="s">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B12" s="21" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="7">
@@ -5662,12 +5613,12 @@
       <c r="H12" s="7">
         <v>8.39185670010494</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="22">
         <v>8.2967958657700525</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="23" t="s">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B13" s="21" t="s">
         <v>50</v>
       </c>
       <c r="C13" s="7">
@@ -5688,12 +5639,12 @@
       <c r="H13" s="7">
         <v>5.8464387750577247</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="22">
         <v>5.8171111599632042</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="23" t="s">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B14" s="21" t="s">
         <v>64</v>
       </c>
       <c r="C14" s="7">
@@ -5714,34 +5665,24 @@
       <c r="H14" s="7">
         <v>6.6795991858443831</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="22">
         <v>6.7226297948554494</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="22"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="19"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="71" t="s">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B15" s="20"/>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B16" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="19"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="25" t="s">
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B17" s="23" t="s">
         <v>86</v>
       </c>
       <c r="C17" s="6" t="s">
@@ -5750,14 +5691,10 @@
       <c r="D17" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="19"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="23" t="s">
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B18" s="21" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -5766,14 +5703,10 @@
       <c r="D18" s="7">
         <v>0.67580221289686704</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B19" s="23" t="s">
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B19" s="21" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -5782,554 +5715,550 @@
       <c r="D19" s="7">
         <v>0.32419778655420278</v>
       </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="19"/>
-    </row>
-    <row r="20" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="26" t="s">
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="2:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="49">
+      <c r="D20" s="47">
         <v>5.4893011563366283E-10</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="29"/>
-    </row>
-    <row r="22" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="30" t="s">
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="27"/>
+    </row>
+    <row r="22" spans="2:18" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B23" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="33"/>
-      <c r="K23" s="78" t="s">
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="31"/>
+      <c r="K23" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="L23" s="31"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="33"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="34" t="s">
+      <c r="L23" s="29"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="31"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B24" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="37"/>
-      <c r="K24" s="34" t="s">
+      <c r="C24" s="33"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="35"/>
+      <c r="K24" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="L24" s="35"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="37"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B25" s="34" t="s">
+      <c r="L24" s="33"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="35"/>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B25" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="37"/>
-      <c r="K25" s="34" t="s">
+      <c r="C25" s="33"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="35"/>
+      <c r="K25" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="L25" s="35"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="37"/>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B26" s="34" t="s">
+      <c r="L25" s="33"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="35"/>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B26" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="37"/>
-      <c r="K26" s="34" t="s">
+      <c r="C26" s="33"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="35"/>
+      <c r="K26" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="L26" s="35"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="37"/>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B27" s="34"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="37"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="37"/>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B28" s="34" t="s">
+      <c r="L26" s="33"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="35"/>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B27" s="32"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="35"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="35"/>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B28" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="36"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="37"/>
-      <c r="K28" s="34" t="s">
+      <c r="D28" s="34"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="35"/>
+      <c r="K28" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="L28" s="35" t="s">
+      <c r="L28" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="M28" s="36"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="37"/>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B29" s="34" t="s">
+      <c r="M28" s="34"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="35"/>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B29" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="33">
         <v>0.6758001745087735</v>
       </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="37"/>
-      <c r="K29" s="34" t="s">
+      <c r="D29" s="34"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="35"/>
+      <c r="K29" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="L29" s="35">
+      <c r="L29" s="33">
         <v>0.33300000000000002</v>
       </c>
-      <c r="M29" s="36"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
-      <c r="R29" s="37"/>
-    </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B30" s="34" t="s">
+      <c r="M29" s="34"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="35"/>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B30" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="33">
         <v>0.32420082549122647</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="37"/>
-      <c r="K30" s="34" t="s">
+      <c r="D30" s="34"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="35"/>
+      <c r="K30" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="33">
         <v>0.33300000000000002</v>
       </c>
-      <c r="M30" s="36"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
-      <c r="R30" s="37"/>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B31" s="34" t="s">
+      <c r="M30" s="34"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="35"/>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B31" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="33">
         <v>0</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="37"/>
-      <c r="K31" s="34" t="s">
+      <c r="D31" s="34"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="35"/>
+      <c r="K31" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="33">
         <v>0.33300000000000002</v>
       </c>
-      <c r="M31" s="36"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="37"/>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B32" s="34" t="s">
+      <c r="M31" s="34"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="35"/>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B32" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="35">
+      <c r="C32" s="33">
         <f>SUM(C29:C31)</f>
         <v>1.0000009999999999</v>
       </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="37"/>
-      <c r="K32" s="34" t="s">
+      <c r="D32" s="34"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="35"/>
+      <c r="K32" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="L32" s="35">
+      <c r="L32" s="33">
         <f>SUM(L29:L31)</f>
         <v>0.99900000000000011</v>
       </c>
-      <c r="M32" s="36"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="37"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B33" s="34"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="37"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="36"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35"/>
-      <c r="P33" s="35"/>
-      <c r="Q33" s="35"/>
-      <c r="R33" s="37"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B34" s="38" t="s">
+      <c r="M32" s="34"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="35"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B33" s="32"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="35"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="35"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B34" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="39">
+      <c r="C34" s="37">
         <f t="shared" ref="C34:I34" si="0">C12*$C$29+C13*$C$30+C14*$C$31</f>
         <v>7.9536292292840196</v>
       </c>
-      <c r="D34" s="39">
+      <c r="D34" s="37">
         <f t="shared" si="0"/>
         <v>7.9105647139099782</v>
       </c>
-      <c r="E34" s="39">
+      <c r="E34" s="37">
         <f t="shared" si="0"/>
         <v>7.8030217082876767</v>
       </c>
-      <c r="F34" s="39">
+      <c r="F34" s="37">
         <f t="shared" si="0"/>
         <v>7.6628322952353551</v>
       </c>
-      <c r="G34" s="39">
+      <c r="G34" s="37">
         <f t="shared" si="0"/>
         <v>7.5879140545194437</v>
       </c>
-      <c r="H34" s="39">
+      <c r="H34" s="37">
         <f t="shared" si="0"/>
         <v>7.5666384994411677</v>
       </c>
-      <c r="I34" s="40">
+      <c r="I34" s="38">
         <f t="shared" si="0"/>
         <v>7.4928883339853689</v>
       </c>
       <c r="J34" s="3"/>
-      <c r="K34" s="48" t="s">
+      <c r="K34" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="L34" s="39">
+      <c r="L34" s="37">
         <f>C12*$L$29+C13*$L$30+C14*$L$31</f>
         <v>7.3787912596949585</v>
       </c>
-      <c r="M34" s="39">
+      <c r="M34" s="37">
         <f t="shared" ref="M34:R34" si="1">D12*$L$29+D13*$L$30+D14*$L$31</f>
         <v>7.3386374751099659</v>
       </c>
-      <c r="N34" s="39">
+      <c r="N34" s="37">
         <f t="shared" si="1"/>
         <v>7.2164956231561419</v>
       </c>
-      <c r="O34" s="39">
+      <c r="O34" s="37">
         <f t="shared" si="1"/>
         <v>7.0907446977655066</v>
       </c>
-      <c r="P34" s="39">
+      <c r="P34" s="37">
         <f t="shared" si="1"/>
         <v>7.0234223245798653</v>
       </c>
-      <c r="Q34" s="39">
+      <c r="Q34" s="37">
         <f t="shared" si="1"/>
         <v>6.9656589221153471</v>
       </c>
-      <c r="R34" s="40">
+      <c r="R34" s="38">
         <f t="shared" si="1"/>
         <v>6.9385667612560393</v>
       </c>
     </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B35" s="34" t="s">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B35" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="37">
         <f>C11-C34</f>
         <v>-0.2125301392486536</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="37">
         <f t="shared" ref="D35:H35" si="2">D11-D34</f>
         <v>-0.1651291036355973</v>
       </c>
-      <c r="E35" s="39">
+      <c r="E35" s="37">
         <f t="shared" si="2"/>
         <v>2.7403909532654147E-2</v>
       </c>
-      <c r="F35" s="39">
+      <c r="F35" s="37">
         <f t="shared" si="2"/>
         <v>6.2939146352596786E-2</v>
       </c>
-      <c r="G35" s="39">
+      <c r="G35" s="37">
         <f t="shared" si="2"/>
         <v>0.13785738706850825</v>
       </c>
-      <c r="H35" s="39">
+      <c r="H35" s="37">
         <f t="shared" si="2"/>
         <v>9.3004455123514518E-2</v>
       </c>
-      <c r="I35" s="40">
+      <c r="I35" s="38">
         <f>I11-I34</f>
         <v>7.549093385115313E-2</v>
       </c>
-      <c r="K35" s="34" t="s">
+      <c r="K35" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="L35" s="39">
+      <c r="L35" s="37">
         <f>C11-L34</f>
         <v>0.36230783034040748</v>
       </c>
-      <c r="M35" s="39">
+      <c r="M35" s="37">
         <f t="shared" ref="M35:R35" si="3">D11-M34</f>
         <v>0.40679813516441499</v>
       </c>
-      <c r="N35" s="39">
+      <c r="N35" s="37">
         <f t="shared" si="3"/>
         <v>0.61392999466418896</v>
       </c>
-      <c r="O35" s="39">
+      <c r="O35" s="37">
         <f t="shared" si="3"/>
         <v>0.63502674382244528</v>
       </c>
-      <c r="P35" s="39">
+      <c r="P35" s="37">
         <f t="shared" si="3"/>
         <v>0.70234911700808667</v>
       </c>
-      <c r="Q35" s="39">
+      <c r="Q35" s="37">
         <f t="shared" si="3"/>
         <v>0.69398403244933515</v>
       </c>
-      <c r="R35" s="40">
+      <c r="R35" s="38">
         <f t="shared" si="3"/>
         <v>0.62981250658048271</v>
       </c>
     </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B36" s="38" t="s">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B36" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="37">
         <f>C35^2</f>
         <v>4.5169060089052089E-2</v>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="37">
         <f t="shared" ref="D36:I36" si="4">D35^2</f>
         <v>2.7267620867495831E-2</v>
       </c>
-      <c r="E36" s="39">
+      <c r="E36" s="37">
         <f t="shared" si="4"/>
         <v>7.5097425767389281E-4</v>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="37">
         <f t="shared" si="4"/>
         <v>3.9613361435935973E-3</v>
       </c>
-      <c r="G36" s="39">
+      <c r="G36" s="37">
         <f t="shared" si="4"/>
         <v>1.9004659169356505E-2</v>
       </c>
-      <c r="H36" s="39">
+      <c r="H36" s="37">
         <f t="shared" si="4"/>
         <v>8.6498286728218261E-3</v>
       </c>
-      <c r="I36" s="40">
+      <c r="I36" s="38">
         <f t="shared" si="4"/>
         <v>5.6988810937191776E-3</v>
       </c>
-      <c r="K36" s="47" t="s">
+      <c r="K36" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="L36" s="39">
+      <c r="L36" s="37">
         <f>L35^2</f>
         <v>0.13126696392597348</v>
       </c>
-      <c r="M36" s="39">
+      <c r="M36" s="37">
         <f t="shared" ref="M36" si="5">M35^2</f>
         <v>0.16548472277324563</v>
       </c>
-      <c r="N36" s="39">
+      <c r="N36" s="37">
         <f t="shared" ref="N36" si="6">N35^2</f>
         <v>0.37691003834837111</v>
       </c>
-      <c r="O36" s="39">
+      <c r="O36" s="37">
         <f t="shared" ref="O36" si="7">O35^2</f>
         <v>0.40325896536973754</v>
       </c>
-      <c r="P36" s="39">
+      <c r="P36" s="37">
         <f t="shared" ref="P36" si="8">P35^2</f>
         <v>0.49329428216203902</v>
       </c>
-      <c r="Q36" s="39">
+      <c r="Q36" s="37">
         <f t="shared" ref="Q36" si="9">Q35^2</f>
         <v>0.48161383729463986</v>
       </c>
-      <c r="R36" s="40">
+      <c r="R36" s="38">
         <f t="shared" ref="R36" si="10">R35^2</f>
         <v>0.39666379344519059</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B37" s="34"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="37"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="35"/>
-      <c r="M37" s="36"/>
-      <c r="N37" s="35"/>
-      <c r="O37" s="35"/>
-      <c r="P37" s="35"/>
-      <c r="Q37" s="35"/>
-      <c r="R37" s="37"/>
-    </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B38" s="38" t="s">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B37" s="32"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="35"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="34"/>
+      <c r="N37" s="33"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="35"/>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B38" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="C38" s="41">
+      <c r="C38" s="39">
         <f>SUM(C36:I36)</f>
         <v>0.11050236029371292</v>
       </c>
-      <c r="D38" s="36"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="37"/>
-      <c r="K38" s="38" t="s">
+      <c r="D38" s="34"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="35"/>
+      <c r="K38" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="L38" s="41">
+      <c r="L38" s="39">
         <f>SUM(L36:R36)</f>
         <v>2.4484926033191972</v>
       </c>
-      <c r="M38" s="36"/>
-      <c r="N38" s="35"/>
-      <c r="O38" s="35"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="35"/>
-      <c r="R38" s="37"/>
-    </row>
-    <row r="39" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="42" t="s">
+      <c r="M38" s="34"/>
+      <c r="N38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33"/>
+      <c r="R38" s="35"/>
+    </row>
+    <row r="39" spans="2:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="C39" s="43">
+      <c r="C39" s="41">
         <f>SQRT(AVERAGE(C36:I36))</f>
         <v>0.12564255437760893</v>
       </c>
-      <c r="D39" s="44"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="46"/>
-      <c r="K39" s="42" t="s">
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="44"/>
+      <c r="K39" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="L39" s="43">
+      <c r="L39" s="41">
         <f>SQRT(AVERAGE(L36:R36))</f>
         <v>0.59142595277602428</v>
       </c>
-      <c r="M39" s="44"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="45"/>
-      <c r="R39" s="46"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B41" s="66" t="s">
+      <c r="M39" s="42"/>
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="44"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B41" s="63" t="s">
         <v>119</v>
       </c>
       <c r="C41" s="4">
@@ -6354,43 +6283,40 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="B1:R41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" style="2" customWidth="1"/>
     <col min="5" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.77734375" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="52" t="s">
+    <row r="1" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B2" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="18"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="76" t="s">
+      <c r="C2" s="14"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B3" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="19"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="53" t="s">
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="50" t="s">
         <v>86</v>
       </c>
       <c r="C4" s="9" t="s">
@@ -6402,13 +6328,10 @@
       <c r="E4" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="19"/>
-    </row>
-    <row r="5" spans="2:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="50" t="s">
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="2:9" ht="30.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="11">
@@ -6420,13 +6343,10 @@
       <c r="E5" s="11">
         <v>0.71480107750477195</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="19"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="50" t="s">
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="11">
@@ -6438,13 +6358,10 @@
       <c r="E6" s="11">
         <v>0.9325909975614225</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="50" t="s">
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="11">
@@ -6456,35 +6373,26 @@
       <c r="E7" s="11">
         <v>1.051645326352604</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="19"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="54"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="73" t="s">
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B8" s="51"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="75"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="55" t="s">
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="71"/>
+    </row>
+    <row r="10" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="52" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -6505,12 +6413,12 @@
       <c r="H10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="55" t="s">
+    <row r="11" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="52" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="7">
@@ -6531,12 +6439,12 @@
       <c r="H11" s="7">
         <v>7.0825485693552999</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="22">
         <v>7.1861443045223252</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="55" t="s">
+    <row r="12" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="52" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="7">
@@ -6557,12 +6465,12 @@
       <c r="H12" s="7">
         <v>6.7464121285733736</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="22">
         <v>6.7867169506050811</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="55" t="s">
+    <row r="13" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="52" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="7">
@@ -6583,12 +6491,12 @@
       <c r="H13" s="7">
         <v>7.4506607962115394</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="22">
         <v>7.4271441334086159</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="55" t="s">
+    <row r="14" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="52" t="s">
         <v>73</v>
       </c>
       <c r="C14" s="7">
@@ -6609,34 +6517,24 @@
       <c r="H14" s="7">
         <v>7.2305631534092916</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="22">
         <v>7.2591161280971006</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="54"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="19"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="71" t="s">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B15" s="51"/>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B16" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="19"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="56" t="s">
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B17" s="53" t="s">
         <v>86</v>
       </c>
       <c r="C17" s="6" t="s">
@@ -6645,14 +6543,10 @@
       <c r="D17" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="19"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="55" t="s">
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" s="52" t="s">
         <v>22</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -6661,14 +6555,10 @@
       <c r="D18" s="7">
         <v>0.31777391101652008</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B19" s="55" t="s">
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="52" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -6677,553 +6567,549 @@
       <c r="D19" s="7">
         <v>0.68222606641491146</v>
       </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="19"/>
-    </row>
-    <row r="20" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="57" t="s">
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="49">
+      <c r="D20" s="47">
         <v>2.2568568492421111E-8</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="29"/>
-    </row>
-    <row r="22" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="30" t="s">
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="27"/>
+    </row>
+    <row r="22" spans="2:18" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B23" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="33"/>
-      <c r="K23" s="78" t="s">
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="31"/>
+      <c r="K23" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="L23" s="31"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="33"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="58"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="37"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="37"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B25" s="58" t="s">
+      <c r="L23" s="29"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="31"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B24" s="55"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="35"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="35"/>
+    </row>
+    <row r="25" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B25" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="37"/>
-      <c r="K25" s="58" t="s">
+      <c r="C25" s="33"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="35"/>
+      <c r="K25" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="L25" s="35"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="37"/>
-    </row>
-    <row r="26" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B26" s="58" t="s">
+      <c r="L25" s="33"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="35"/>
+    </row>
+    <row r="26" spans="2:18" ht="32" x14ac:dyDescent="0.2">
+      <c r="B26" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="37"/>
-      <c r="K26" s="58" t="s">
+      <c r="C26" s="33"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="35"/>
+      <c r="K26" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="L26" s="35"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="37"/>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B27" s="58" t="s">
+      <c r="L26" s="33"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="35"/>
+    </row>
+    <row r="27" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B27" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="37"/>
-      <c r="K27" s="58" t="s">
+      <c r="C27" s="33"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="35"/>
+      <c r="K27" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="L27" s="35"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="37"/>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B28" s="58"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="37"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="37"/>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B29" s="58" t="s">
+      <c r="L27" s="33"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="35"/>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B28" s="55"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="35"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="35"/>
+    </row>
+    <row r="29" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B29" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="37"/>
-      <c r="K29" s="58" t="s">
+      <c r="D29" s="34"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="35"/>
+      <c r="K29" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="L29" s="35" t="s">
+      <c r="L29" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="M29" s="36"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
-      <c r="R29" s="37"/>
-    </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B30" s="58" t="s">
+      <c r="M29" s="34"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="35"/>
+    </row>
+    <row r="30" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B30" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="33">
         <v>0.68222505771782804</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="37"/>
-      <c r="K30" s="58" t="s">
+      <c r="D30" s="34"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="35"/>
+      <c r="K30" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="33">
         <v>0.33300000000000002</v>
       </c>
-      <c r="M30" s="36"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
-      <c r="R30" s="37"/>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B31" s="58" t="s">
+      <c r="M30" s="34"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="35"/>
+    </row>
+    <row r="31" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B31" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="33">
         <v>0.31777494228220149</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="37"/>
-      <c r="K31" s="58" t="s">
+      <c r="D31" s="34"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="35"/>
+      <c r="K31" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="33">
         <v>0.33300000000000002</v>
       </c>
-      <c r="M31" s="36"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="37"/>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B32" s="58" t="s">
+      <c r="M31" s="34"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="35"/>
+    </row>
+    <row r="32" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B32" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="35">
+      <c r="C32" s="33">
         <v>0</v>
       </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="37"/>
-      <c r="K32" s="58" t="s">
+      <c r="D32" s="34"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="35"/>
+      <c r="K32" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="L32" s="35">
+      <c r="L32" s="33">
         <v>0.33300000000000002</v>
       </c>
-      <c r="M32" s="36"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="37"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B33" s="58" t="s">
+      <c r="M32" s="34"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="35"/>
+    </row>
+    <row r="33" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="33">
         <f>SUM(C30:C32)</f>
         <v>1.0000000000000295</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="37"/>
-      <c r="K33" s="58" t="s">
+      <c r="D33" s="34"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="35"/>
+      <c r="K33" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="33">
         <f>SUM(L30:L32)</f>
         <v>0.99900000000000011</v>
       </c>
-      <c r="M33" s="36"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35"/>
-      <c r="P33" s="35"/>
-      <c r="Q33" s="35"/>
-      <c r="R33" s="37"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B34" s="59"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="40"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="35"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B34" s="56"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="38"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="59"/>
-      <c r="L34" s="39"/>
-      <c r="M34" s="39"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="39"/>
-      <c r="Q34" s="39"/>
-      <c r="R34" s="40"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B35" s="58" t="s">
+      <c r="K34" s="56"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
+      <c r="N34" s="37"/>
+      <c r="O34" s="37"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="37"/>
+      <c r="R34" s="38"/>
+    </row>
+    <row r="35" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B35" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="37">
         <f>$C$30*C12+C13*$C$31+C14*$C$32</f>
         <v>6.7213067735744323</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="37">
         <f t="shared" ref="D35:I35" si="0">$C$30*D12+D13*$C$31+D14*$C$32</f>
         <v>6.8483372466913011</v>
       </c>
-      <c r="E35" s="39">
+      <c r="E35" s="37">
         <f>$C$30*E12+E13*$C$31+E14*$C$32</f>
         <v>6.9911110139360098</v>
       </c>
-      <c r="F35" s="39">
+      <c r="F35" s="37">
         <f>$C$30*F12+F13*$C$31+F14*$C$32</f>
         <v>6.9748180039061634</v>
       </c>
-      <c r="G35" s="39">
+      <c r="G35" s="37">
         <f t="shared" si="0"/>
         <v>6.9085252808327953</v>
       </c>
-      <c r="H35" s="39">
+      <c r="H35" s="37">
         <f>$C$30*H12+H13*$C$31+H14*$C$32</f>
         <v>6.9702047082846086</v>
       </c>
-      <c r="I35" s="39">
+      <c r="I35" s="37">
         <f t="shared" si="0"/>
         <v>6.9902286616566274</v>
       </c>
-      <c r="K35" s="58" t="s">
+      <c r="K35" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="L35" s="39">
+      <c r="L35" s="37">
         <f>$L$30*C12+C13*$L$31+C14*$L$32</f>
         <v>6.9206180148103051</v>
       </c>
-      <c r="M35" s="39">
+      <c r="M35" s="37">
         <f t="shared" ref="M35:R35" si="1">$L$30*D12+D13*$L$31+D14*$L$32</f>
         <v>7.0393947637212317</v>
       </c>
-      <c r="N35" s="39">
+      <c r="N35" s="37">
         <f t="shared" si="1"/>
         <v>7.1244746943036237</v>
       </c>
-      <c r="O35" s="39">
+      <c r="O35" s="37">
         <f t="shared" si="1"/>
         <v>7.1084112923502421</v>
       </c>
-      <c r="P35" s="39">
+      <c r="P35" s="37">
         <f t="shared" si="1"/>
         <v>7.1141179859235155</v>
       </c>
-      <c r="Q35" s="39">
+      <c r="Q35" s="37">
         <f t="shared" si="1"/>
         <v>7.1354028140386703</v>
       </c>
-      <c r="R35" s="39">
+      <c r="R35" s="37">
         <f t="shared" si="1"/>
         <v>7.150501411632896</v>
       </c>
     </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B36" s="59" t="s">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B36" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="37">
         <f>C11-C35</f>
         <v>-0.30620981440283668</v>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="37">
         <f t="shared" ref="D36:I36" si="2">D11-D35</f>
         <v>-9.0242742263569653E-2</v>
       </c>
-      <c r="E36" s="39">
+      <c r="E36" s="37">
         <f t="shared" si="2"/>
         <v>2.6395129005246432E-2</v>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="37">
         <f t="shared" si="2"/>
         <v>2.460446360179791E-2</v>
       </c>
-      <c r="G36" s="39">
+      <c r="G36" s="37">
         <f t="shared" si="2"/>
         <v>9.5448855889884499E-2</v>
       </c>
-      <c r="H36" s="39">
+      <c r="H36" s="37">
         <f t="shared" si="2"/>
         <v>0.11234386107069128</v>
       </c>
-      <c r="I36" s="39">
+      <c r="I36" s="37">
         <f t="shared" si="2"/>
         <v>0.19591564286569785</v>
       </c>
-      <c r="K36" s="59" t="s">
+      <c r="K36" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="L36" s="39">
+      <c r="L36" s="37">
         <f>C11-L35</f>
         <v>-0.50552105563870953</v>
       </c>
-      <c r="M36" s="39">
+      <c r="M36" s="37">
         <f t="shared" ref="M36:R36" si="3">D11-M35</f>
         <v>-0.28130025929350033</v>
       </c>
-      <c r="N36" s="39">
+      <c r="N36" s="37">
         <f t="shared" si="3"/>
         <v>-0.10696855136236749</v>
       </c>
-      <c r="O36" s="39">
+      <c r="O36" s="37">
         <f t="shared" si="3"/>
         <v>-0.10898882484228078</v>
       </c>
-      <c r="P36" s="39">
+      <c r="P36" s="37">
         <f t="shared" si="3"/>
         <v>-0.11014384920083575</v>
       </c>
-      <c r="Q36" s="39">
+      <c r="Q36" s="37">
         <f t="shared" si="3"/>
         <v>-5.285424468337041E-2</v>
       </c>
-      <c r="R36" s="40">
+      <c r="R36" s="38">
         <f t="shared" si="3"/>
         <v>3.5642892889429234E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B37" s="58" t="s">
+    <row r="37" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B37" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="C37" s="61">
+      <c r="C37" s="58">
         <f>C36^2</f>
         <v>9.3764450436619684E-2</v>
       </c>
-      <c r="D37" s="61">
+      <c r="D37" s="58">
         <f t="shared" ref="D37:I37" si="4">D36^2</f>
         <v>8.143752531249061E-3</v>
       </c>
-      <c r="E37" s="61">
+      <c r="E37" s="58">
         <f t="shared" si="4"/>
         <v>6.9670283520360148E-4</v>
       </c>
-      <c r="F37" s="61">
+      <c r="F37" s="58">
         <f t="shared" si="4"/>
         <v>6.0537962913219823E-4</v>
       </c>
-      <c r="G37" s="61">
+      <c r="G37" s="58">
         <f t="shared" si="4"/>
         <v>9.1104840906879384E-3</v>
       </c>
-      <c r="H37" s="61">
+      <c r="H37" s="58">
         <f t="shared" si="4"/>
         <v>1.2621143120270783E-2</v>
       </c>
-      <c r="I37" s="61">
+      <c r="I37" s="58">
         <f t="shared" si="4"/>
         <v>3.8382939119479667E-2</v>
       </c>
-      <c r="K37" s="58" t="s">
+      <c r="K37" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="L37" s="61">
+      <c r="L37" s="58">
         <f>L36^2</f>
         <v>0.25555153769407524</v>
       </c>
-      <c r="M37" s="61">
+      <c r="M37" s="58">
         <f t="shared" ref="M37" si="5">M36^2</f>
         <v>7.9129835878590515E-2</v>
       </c>
-      <c r="N37" s="61">
+      <c r="N37" s="58">
         <f t="shared" ref="N37" si="6">N36^2</f>
         <v>1.1442270980563453E-2</v>
       </c>
-      <c r="O37" s="61">
+      <c r="O37" s="58">
         <f t="shared" ref="O37" si="7">O36^2</f>
         <v>1.1878563940501361E-2</v>
       </c>
-      <c r="P37" s="61">
+      <c r="P37" s="58">
         <f t="shared" ref="P37" si="8">P36^2</f>
         <v>1.2131667516776447E-2</v>
       </c>
-      <c r="Q37" s="61">
+      <c r="Q37" s="58">
         <f t="shared" ref="Q37" si="9">Q36^2</f>
         <v>2.7935711810495893E-3</v>
       </c>
-      <c r="R37" s="63">
+      <c r="R37" s="60">
         <f t="shared" ref="R37" si="10">R36^2</f>
         <v>1.2704158135273251E-3</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B38" s="59" t="s">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B38" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="41">
+      <c r="C38" s="39">
         <f>SUM(C37:I37)</f>
         <v>0.16332485176264294</v>
       </c>
-      <c r="D38" s="36"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="37"/>
-      <c r="K38" s="59" t="s">
+      <c r="D38" s="34"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="35"/>
+      <c r="K38" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="L38" s="41">
+      <c r="L38" s="39">
         <f>SUM(L37:R37)</f>
         <v>0.37419786300508395</v>
       </c>
-      <c r="M38" s="36"/>
-      <c r="N38" s="35"/>
-      <c r="O38" s="35"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="35"/>
-      <c r="R38" s="37"/>
-    </row>
-    <row r="39" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="60" t="s">
+      <c r="M38" s="34"/>
+      <c r="N38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33"/>
+      <c r="R38" s="35"/>
+    </row>
+    <row r="39" spans="2:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="C39" s="62">
+      <c r="C39" s="59">
         <f>SQRT(AVERAGE(C37:I37))</f>
         <v>0.15274855704843029</v>
       </c>
-      <c r="D39" s="44"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="46"/>
-      <c r="K39" s="60" t="s">
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="44"/>
+      <c r="K39" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="L39" s="62">
+      <c r="L39" s="59">
         <f>SQRT(AVERAGE(L37:R37))</f>
         <v>0.23120734757389275</v>
       </c>
-      <c r="M39" s="44"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="45"/>
-      <c r="R39" s="46"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="M39" s="42"/>
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="44"/>
+    </row>
+    <row r="41" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>119</v>
       </c>
@@ -7248,43 +7134,40 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="B1:R41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" style="2" customWidth="1"/>
     <col min="5" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.77734375" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="52" t="s">
+    <row r="1" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B2" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="18"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="76" t="s">
+      <c r="C2" s="14"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B3" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="19"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="53" t="s">
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="50" t="s">
         <v>86</v>
       </c>
       <c r="C4" s="9" t="s">
@@ -7296,13 +7179,10 @@
       <c r="E4" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="19"/>
-    </row>
-    <row r="5" spans="2:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="50" t="s">
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="2:9" ht="30.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="48" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="11">
@@ -7314,13 +7194,10 @@
       <c r="E5" s="11">
         <v>1.313773130643523</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="19"/>
-    </row>
-    <row r="6" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="50" t="s">
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="2:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="B6" s="48" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="11">
@@ -7332,13 +7209,10 @@
       <c r="E6" s="11">
         <v>2.120359351148926</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="50" t="s">
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="48" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="11">
@@ -7350,35 +7224,26 @@
       <c r="E7" s="11">
         <v>2.232442595052639</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="19"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="54"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="73" t="s">
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B8" s="51"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="75"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="55" t="s">
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="71"/>
+    </row>
+    <row r="10" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="52" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -7399,12 +7264,12 @@
       <c r="H10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="55" t="s">
+    <row r="11" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="52" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="7">
@@ -7425,12 +7290,12 @@
       <c r="H11" s="7">
         <v>6.2747620212419388</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="22">
         <v>6.1548580940164177</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="55" t="s">
+    <row r="12" spans="2:9" ht="19.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="52" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="7">
@@ -7451,12 +7316,12 @@
       <c r="H12" s="7">
         <v>7.4506607962115394</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="22">
         <v>7.4271441334086159</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="55" t="s">
+    <row r="13" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="52" t="s">
         <v>54</v>
       </c>
       <c r="C13" s="7">
@@ -7477,12 +7342,12 @@
       <c r="H13" s="7">
         <v>5.3278761687895813</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="22">
         <v>5.1704839950381514</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="55" t="s">
+    <row r="14" spans="2:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="B14" s="52" t="s">
         <v>77</v>
       </c>
       <c r="C14" s="7">
@@ -7503,34 +7368,24 @@
       <c r="H14" s="7">
         <v>5.2781146592305168</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="22">
         <v>5.1704839950381514</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="54"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="19"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="71" t="s">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B15" s="51"/>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B16" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="19"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="56" t="s">
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B17" s="53" t="s">
         <v>86</v>
       </c>
       <c r="C17" s="6" t="s">
@@ -7539,14 +7394,10 @@
       <c r="D17" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="19"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="55" t="s">
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" s="52" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -7555,14 +7406,10 @@
       <c r="D18" s="7">
         <v>0.45973532226379249</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B19" s="55" t="s">
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="52" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -7571,553 +7418,549 @@
       <c r="D19" s="7">
         <v>8.0865157072275651E-2</v>
       </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="19"/>
-    </row>
-    <row r="20" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="57" t="s">
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="49">
+      <c r="D20" s="47">
         <v>0.45939952066393192</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="29"/>
-    </row>
-    <row r="22" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="30" t="s">
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="27"/>
+    </row>
+    <row r="22" spans="2:18" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B23" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="33"/>
-      <c r="K23" s="78" t="s">
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="31"/>
+      <c r="K23" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="L23" s="31"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="33"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="58"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="37"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="37"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B25" s="58" t="s">
+      <c r="L23" s="29"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="31"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B24" s="55"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="35"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="35"/>
+    </row>
+    <row r="25" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B25" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="37"/>
-      <c r="K25" s="58" t="s">
+      <c r="C25" s="33"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="35"/>
+      <c r="K25" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="L25" s="35"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="37"/>
-    </row>
-    <row r="26" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B26" s="58" t="s">
+      <c r="L25" s="33"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="35"/>
+    </row>
+    <row r="26" spans="2:18" ht="32" x14ac:dyDescent="0.2">
+      <c r="B26" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="37"/>
-      <c r="K26" s="58" t="s">
+      <c r="C26" s="33"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="35"/>
+      <c r="K26" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="L26" s="35"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="37"/>
-    </row>
-    <row r="27" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B27" s="58" t="s">
+      <c r="L26" s="33"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="35"/>
+    </row>
+    <row r="27" spans="2:18" ht="32" x14ac:dyDescent="0.2">
+      <c r="B27" s="55" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="37"/>
-      <c r="K27" s="58" t="s">
+      <c r="C27" s="33"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="35"/>
+      <c r="K27" s="55" t="s">
         <v>118</v>
       </c>
-      <c r="L27" s="35"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="37"/>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B28" s="58"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="37"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="37"/>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B29" s="58" t="s">
+      <c r="L27" s="33"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="35"/>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B28" s="55"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="35"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="35"/>
+    </row>
+    <row r="29" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B29" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="37"/>
-      <c r="K29" s="58" t="s">
+      <c r="D29" s="34"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="35"/>
+      <c r="K29" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="L29" s="35" t="s">
+      <c r="L29" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="M29" s="36"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
-      <c r="R29" s="37"/>
-    </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B30" s="58" t="s">
+      <c r="M29" s="34"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="35"/>
+    </row>
+    <row r="30" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B30" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="33">
         <v>0.45939567508331203</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="37"/>
-      <c r="K30" s="58" t="s">
+      <c r="D30" s="34"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="35"/>
+      <c r="K30" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="33">
         <v>0.33300000000000002</v>
       </c>
-      <c r="M30" s="36"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
-      <c r="R30" s="37"/>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B31" s="58" t="s">
+      <c r="M30" s="34"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="35"/>
+    </row>
+    <row r="31" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B31" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="33">
         <v>0.45840328589011387</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="37"/>
-      <c r="K31" s="58" t="s">
+      <c r="D31" s="34"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="35"/>
+      <c r="K31" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="33">
         <v>0.33300000000000002</v>
       </c>
-      <c r="M31" s="36"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="37"/>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B32" s="58" t="s">
+      <c r="M31" s="34"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="35"/>
+    </row>
+    <row r="32" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B32" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="35">
+      <c r="C32" s="33">
         <v>8.2201039026603986E-2</v>
       </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="37"/>
-      <c r="K32" s="58" t="s">
+      <c r="D32" s="34"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="35"/>
+      <c r="K32" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="L32" s="35">
+      <c r="L32" s="33">
         <v>0.33300000000000002</v>
       </c>
-      <c r="M32" s="36"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="37"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B33" s="58" t="s">
+      <c r="M32" s="34"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="35"/>
+    </row>
+    <row r="33" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="33">
         <f>SUM(C30:C32)</f>
         <v>1.0000000000000298</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="37"/>
-      <c r="K33" s="58" t="s">
+      <c r="D33" s="34"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="35"/>
+      <c r="K33" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="33">
         <f>SUM(L30:L32)</f>
         <v>0.99900000000000011</v>
       </c>
-      <c r="M33" s="36"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35"/>
-      <c r="P33" s="35"/>
-      <c r="Q33" s="35"/>
-      <c r="R33" s="37"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B34" s="59"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="40"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="35"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B34" s="56"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="38"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="59"/>
-      <c r="L34" s="39"/>
-      <c r="M34" s="39"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="39"/>
-      <c r="Q34" s="39"/>
-      <c r="R34" s="40"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B35" s="58" t="s">
+      <c r="K34" s="56"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
+      <c r="N34" s="37"/>
+      <c r="O34" s="37"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="37"/>
+      <c r="R34" s="38"/>
+    </row>
+    <row r="35" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B35" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="37">
         <f>$C$30*C12+C13*$C$31+C14*$C$32</f>
         <v>6.1276234938128002</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="37">
         <f t="shared" ref="D35:I35" si="0">$C$30*D12+D13*$C$31+D14*$C$32</f>
         <v>6.199436612482323</v>
       </c>
-      <c r="E35" s="39">
+      <c r="E35" s="37">
         <f>$C$30*E12+E13*$C$31+E14*$C$32</f>
         <v>6.276988608036258</v>
       </c>
-      <c r="F35" s="39">
+      <c r="F35" s="37">
         <f>$C$30*F12+F13*$C$31+F14*$C$32</f>
         <v>6.2325220803764578</v>
       </c>
-      <c r="G35" s="39">
+      <c r="G35" s="37">
         <f t="shared" si="0"/>
         <v>6.3052355464061867</v>
       </c>
-      <c r="H35" s="39">
+      <c r="H35" s="37">
         <f>$C$30*H12+H13*$C$31+H14*$C$32</f>
         <v>6.2989837979714407</v>
       </c>
-      <c r="I35" s="40">
+      <c r="I35" s="38">
         <f t="shared" si="0"/>
         <v>6.2071839027386062</v>
       </c>
-      <c r="K35" s="58" t="s">
+      <c r="K35" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="L35" s="39">
+      <c r="L35" s="37">
         <f>$L$30*C12+C13*$L$31+C14*$L$32</f>
         <v>5.8512308053194246</v>
       </c>
-      <c r="M35" s="39">
+      <c r="M35" s="37">
         <f t="shared" ref="M35:R35" si="1">$L$30*D12+D13*$L$31+D14*$L$32</f>
         <v>5.9607762135369162</v>
       </c>
-      <c r="N35" s="39">
+      <c r="N35" s="37">
         <f t="shared" si="1"/>
         <v>6.0105269990197439</v>
       </c>
-      <c r="O35" s="39">
+      <c r="O35" s="37">
         <f t="shared" si="1"/>
         <v>5.9503166016240048</v>
       </c>
-      <c r="P35" s="39">
+      <c r="P35" s="37">
         <f t="shared" si="1"/>
         <v>6.03757651332013</v>
       </c>
-      <c r="Q35" s="39">
+      <c r="Q35" s="37">
         <f t="shared" si="1"/>
         <v>6.0128649908691356</v>
       </c>
-      <c r="R35" s="40">
+      <c r="R35" s="38">
         <f t="shared" si="1"/>
         <v>5.9167813371204785</v>
       </c>
     </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B36" s="59" t="s">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B36" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="37">
         <f>C11-C35</f>
         <v>1.6562140312845308E-2</v>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="37">
         <f t="shared" ref="D36:I36" si="2">D11-D35</f>
         <v>7.1393142426048328E-3</v>
       </c>
-      <c r="E36" s="39">
+      <c r="E36" s="37">
         <f t="shared" si="2"/>
         <v>-2.1238566282891114E-2</v>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="37">
         <f t="shared" si="2"/>
         <v>7.0096895368447321E-2</v>
       </c>
-      <c r="G36" s="39">
+      <c r="G36" s="37">
         <f t="shared" si="2"/>
         <v>6.4992627467281849E-3</v>
       </c>
-      <c r="H36" s="39">
+      <c r="H36" s="37">
         <f t="shared" si="2"/>
         <v>-2.4221776729501876E-2</v>
       </c>
-      <c r="I36" s="40">
+      <c r="I36" s="38">
         <f t="shared" si="2"/>
         <v>-5.2325808722188505E-2</v>
       </c>
-      <c r="K36" s="59" t="s">
+      <c r="K36" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="L36" s="39">
+      <c r="L36" s="37">
         <f>C11-L35</f>
         <v>0.29295482880622092</v>
       </c>
-      <c r="M36" s="39">
+      <c r="M36" s="37">
         <f t="shared" ref="M36:R36" si="3">D11-M35</f>
         <v>0.24579971318801164</v>
       </c>
-      <c r="N36" s="39">
+      <c r="N36" s="37">
         <f t="shared" si="3"/>
         <v>0.24522304273362305</v>
       </c>
-      <c r="O36" s="39">
+      <c r="O36" s="37">
         <f t="shared" si="3"/>
         <v>0.35230237412090037</v>
       </c>
-      <c r="P36" s="39">
+      <c r="P36" s="37">
         <f t="shared" si="3"/>
         <v>0.27415829583278484</v>
       </c>
-      <c r="Q36" s="39">
+      <c r="Q36" s="37">
         <f t="shared" si="3"/>
         <v>0.26189703037280321</v>
       </c>
-      <c r="R36" s="40">
+      <c r="R36" s="38">
         <f t="shared" si="3"/>
         <v>0.23807675689593921</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B37" s="58" t="s">
+    <row r="37" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B37" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="C37" s="61">
+      <c r="C37" s="58">
         <f>C36^2</f>
         <v>2.7430449174237567E-4</v>
       </c>
-      <c r="D37" s="61">
+      <c r="D37" s="58">
         <f t="shared" ref="D37:I37" si="4">D36^2</f>
         <v>5.0969807854660215E-5</v>
       </c>
-      <c r="E37" s="61">
+      <c r="E37" s="58">
         <f t="shared" si="4"/>
         <v>4.5107669775275923E-4</v>
       </c>
-      <c r="F37" s="61">
+      <c r="F37" s="58">
         <f t="shared" si="4"/>
         <v>4.9135747402950514E-3</v>
       </c>
-      <c r="G37" s="61">
+      <c r="G37" s="58">
         <f t="shared" si="4"/>
         <v>4.2240416251008788E-5</v>
       </c>
-      <c r="H37" s="61">
+      <c r="H37" s="58">
         <f t="shared" si="4"/>
         <v>5.8669446793383861E-4</v>
       </c>
-      <c r="I37" s="63">
+      <c r="I37" s="60">
         <f t="shared" si="4"/>
         <v>2.7379902584310587E-3</v>
       </c>
-      <c r="K37" s="58" t="s">
+      <c r="K37" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="L37" s="61">
+      <c r="L37" s="58">
         <f>L36^2</f>
         <v>8.5822531720882209E-2</v>
       </c>
-      <c r="M37" s="61">
+      <c r="M37" s="58">
         <f t="shared" ref="M37:R37" si="5">M36^2</f>
         <v>6.0417499003308783E-2</v>
       </c>
-      <c r="N37" s="61">
+      <c r="N37" s="58">
         <f t="shared" si="5"/>
         <v>6.0134340687536321E-2</v>
       </c>
-      <c r="O37" s="61">
+      <c r="O37" s="58">
         <f t="shared" si="5"/>
         <v>0.12411696281122285</v>
       </c>
-      <c r="P37" s="61">
+      <c r="P37" s="58">
         <f t="shared" si="5"/>
         <v>7.5162771173936771E-2</v>
       </c>
-      <c r="Q37" s="61">
+      <c r="Q37" s="58">
         <f t="shared" si="5"/>
         <v>6.859005451809301E-2</v>
       </c>
-      <c r="R37" s="63">
+      <c r="R37" s="60">
         <f t="shared" si="5"/>
         <v>5.668054217408814E-2</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B38" s="59" t="s">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B38" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="41">
+      <c r="C38" s="39">
         <f>SUM(C37:I37)</f>
         <v>9.0568508802607531E-3</v>
       </c>
-      <c r="D38" s="36"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="37"/>
-      <c r="K38" s="59" t="s">
+      <c r="D38" s="34"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="35"/>
+      <c r="K38" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="L38" s="41">
+      <c r="L38" s="39">
         <f>SUM(L37:R37)</f>
         <v>0.53092470208906817</v>
       </c>
-      <c r="M38" s="36"/>
-      <c r="N38" s="35"/>
-      <c r="O38" s="35"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="35"/>
-      <c r="R38" s="37"/>
-    </row>
-    <row r="39" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="60" t="s">
+      <c r="M38" s="34"/>
+      <c r="N38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33"/>
+      <c r="R38" s="35"/>
+    </row>
+    <row r="39" spans="2:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="C39" s="62">
+      <c r="C39" s="59">
         <f>SQRT(AVERAGE(C37:I37))</f>
         <v>3.5969929664057591E-2</v>
       </c>
-      <c r="D39" s="44"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="46"/>
-      <c r="K39" s="60" t="s">
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="44"/>
+      <c r="K39" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="L39" s="62">
+      <c r="L39" s="59">
         <f>SQRT(AVERAGE(L37:R37))</f>
         <v>0.2754022258674102</v>
       </c>
-      <c r="M39" s="44"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="45"/>
-      <c r="R39" s="46"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="M39" s="42"/>
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="44"/>
+    </row>
+    <row r="41" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>119</v>
       </c>
@@ -8139,36 +7982,36 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42DB33B3-C885-4F67-96C0-C3B576B26AD9}">
   <dimension ref="A1:S65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="7" max="7" width="18.109375" customWidth="1"/>
-    <col min="17" max="17" width="12.21875" customWidth="1"/>
-    <col min="19" max="19" width="12.109375" customWidth="1"/>
+    <col min="7" max="7" width="18.1640625" customWidth="1"/>
+    <col min="17" max="17" width="12.1640625" customWidth="1"/>
+    <col min="19" max="19" width="12.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="55" t="s">
+    <row r="2" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="A2" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="52" t="s">
         <v>77</v>
       </c>
       <c r="G2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>6.1441856341256456</v>
       </c>
@@ -8182,7 +8025,7 @@
         <v>5.1416635565026603</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>6.2065759267249279</v>
       </c>
@@ -8195,12 +8038,12 @@
       <c r="D4" s="8">
         <v>5.3518581334760666</v>
       </c>
-      <c r="G4" s="70" t="s">
+      <c r="G4" s="65" t="s">
         <v>121</v>
       </c>
-      <c r="H4" s="70"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H4" s="65"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>6.2557500417533669</v>
       </c>
@@ -8213,14 +8056,14 @@
       <c r="D5" s="7">
         <v>5.3278761687895813</v>
       </c>
-      <c r="G5" s="67" t="s">
+      <c r="G5" t="s">
         <v>122</v>
       </c>
-      <c r="H5" s="67">
+      <c r="H5">
         <v>0.86290520914814961</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>6.3026189757449051</v>
       </c>
@@ -8233,14 +8076,14 @@
       <c r="D6" s="7">
         <v>5.2257466737132017</v>
       </c>
-      <c r="G6" s="67" t="s">
+      <c r="G6" t="s">
         <v>123</v>
       </c>
-      <c r="H6" s="67">
+      <c r="H6">
         <v>0.74460539997501185</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>6.3117348091529148</v>
       </c>
@@ -8253,14 +8096,14 @@
       <c r="D7" s="7">
         <v>5.3518581334760666</v>
       </c>
-      <c r="G7" s="67" t="s">
+      <c r="G7" t="s">
         <v>124</v>
       </c>
-      <c r="H7" s="67">
+      <c r="H7">
         <v>0.48921079995002376</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>6.2747620212419388</v>
       </c>
@@ -8273,168 +8116,166 @@
       <c r="D8" s="7">
         <v>5.2781146592305168</v>
       </c>
-      <c r="G8" s="67" t="s">
+      <c r="G8" t="s">
         <v>125</v>
       </c>
-      <c r="H8" s="67">
+      <c r="H8">
         <v>4.877564898742489E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="24">
+    <row r="9" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22">
         <v>6.1548580940164177</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="22">
         <v>7.4271441334086159</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="22">
         <v>5.1704839950381514</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="22">
         <v>5.1704839950381514</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="H9" s="68">
+      <c r="H9" s="26">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G12" s="69"/>
-      <c r="H12" s="69" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G12" s="64"/>
+      <c r="H12" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="I12" s="69" t="s">
+      <c r="I12" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="J12" s="69" t="s">
+      <c r="J12" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="K12" s="69" t="s">
+      <c r="K12" s="64" t="s">
         <v>135</v>
       </c>
-      <c r="L12" s="69" t="s">
+      <c r="L12" s="64" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G13" s="67" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G13" t="s">
         <v>128</v>
       </c>
-      <c r="H13" s="67">
+      <c r="H13">
         <v>3</v>
       </c>
-      <c r="I13" s="67">
+      <c r="I13">
         <v>2.0808550988272129E-2</v>
       </c>
-      <c r="J13" s="67">
+      <c r="J13">
         <v>6.9361836627573762E-3</v>
       </c>
-      <c r="K13" s="67">
+      <c r="K13">
         <v>2.9155095679476331</v>
       </c>
-      <c r="L13" s="67">
+      <c r="L13">
         <v>0.20147069597019612</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G14" s="67" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G14" t="s">
         <v>129</v>
       </c>
-      <c r="H14" s="67">
+      <c r="H14">
         <v>3</v>
       </c>
-      <c r="I14" s="67">
+      <c r="I14">
         <v>7.1371918024334471E-3</v>
       </c>
-      <c r="J14" s="67">
+      <c r="J14">
         <v>2.3790639341444825E-3</v>
       </c>
-      <c r="K14" s="67"/>
-      <c r="L14" s="67"/>
-    </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G15" s="68" t="s">
+    </row>
+    <row r="15" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G15" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="H15" s="68">
+      <c r="H15" s="26">
         <v>6</v>
       </c>
-      <c r="I15" s="68">
+      <c r="I15" s="26">
         <v>2.7945742790705577E-2</v>
       </c>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="68"/>
-    </row>
-    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G17" s="69"/>
-      <c r="H17" s="69" t="s">
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+    </row>
+    <row r="16" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="G17" s="64"/>
+      <c r="H17" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="I17" s="69" t="s">
+      <c r="I17" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="J17" s="69" t="s">
+      <c r="J17" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="K17" s="69" t="s">
+      <c r="K17" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="L17" s="69" t="s">
+      <c r="L17" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="M17" s="69" t="s">
+      <c r="M17" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="N17" s="69" t="s">
+      <c r="N17" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="O17" s="69" t="s">
+      <c r="O17" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="Q17" s="71" t="s">
+      <c r="Q17" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="R17" s="72"/>
-      <c r="S17" s="72"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G18" s="67" t="s">
+      <c r="R17" s="73"/>
+      <c r="S17" s="73"/>
+    </row>
+    <row r="18" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="G18" t="s">
         <v>131</v>
       </c>
-      <c r="H18" s="67">
+      <c r="H18">
         <v>1.7120617507696769</v>
       </c>
-      <c r="I18" s="67">
+      <c r="I18">
         <v>2.3234250580078584</v>
       </c>
-      <c r="J18" s="67">
+      <c r="J18">
         <v>0.73686979697017896</v>
       </c>
-      <c r="K18" s="67">
+      <c r="K18">
         <v>0.51459709573416323</v>
       </c>
-      <c r="L18" s="67">
+      <c r="L18">
         <v>-5.6821137406910198</v>
       </c>
-      <c r="M18" s="67">
+      <c r="M18">
         <v>9.1062372422303746</v>
       </c>
-      <c r="N18" s="67">
+      <c r="N18">
         <v>-5.6821137406910198</v>
       </c>
-      <c r="O18" s="67">
+      <c r="O18">
         <v>9.1062372422303746</v>
       </c>
-      <c r="Q18" s="56" t="s">
+      <c r="Q18" s="53" t="s">
         <v>86</v>
       </c>
       <c r="R18" s="6" t="s">
@@ -8444,35 +8285,35 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G19" s="67" t="s">
+    <row r="19" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="G19" t="s">
         <v>42</v>
       </c>
-      <c r="H19" s="67">
+      <c r="H19">
         <v>0.11181418771210382</v>
       </c>
-      <c r="I19" s="67">
+      <c r="I19">
         <v>0.38727905935494056</v>
       </c>
-      <c r="J19" s="67">
+      <c r="J19">
         <v>0.28871736028884099</v>
       </c>
-      <c r="K19" s="67">
+      <c r="K19">
         <v>0.79159806290232615</v>
       </c>
-      <c r="L19" s="67">
+      <c r="L19">
         <v>-1.1206806238457772</v>
       </c>
-      <c r="M19" s="67">
+      <c r="M19">
         <v>1.3443089992699846</v>
       </c>
-      <c r="N19" s="67">
+      <c r="N19">
         <v>-1.1206806238457772</v>
       </c>
-      <c r="O19" s="67">
+      <c r="O19">
         <v>1.3443089992699846</v>
       </c>
-      <c r="Q19" s="55" t="s">
+      <c r="Q19" s="52" t="s">
         <v>23</v>
       </c>
       <c r="R19" s="7" t="s">
@@ -8482,35 +8323,35 @@
         <v>0.45973532226379249</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G20" s="67" t="s">
+    <row r="20" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="G20" t="s">
         <v>54</v>
       </c>
-      <c r="H20" s="67">
+      <c r="H20">
         <v>0.63049883399917306</v>
       </c>
-      <c r="I20" s="67">
+      <c r="I20">
         <v>0.39259230689446123</v>
       </c>
-      <c r="J20" s="67">
+      <c r="J20">
         <v>1.6059887647484319</v>
       </c>
-      <c r="K20" s="67">
+      <c r="K20">
         <v>0.20662749118486082</v>
       </c>
-      <c r="L20" s="67">
+      <c r="L20">
         <v>-0.61890510255991305</v>
       </c>
-      <c r="M20" s="67">
+      <c r="M20">
         <v>1.8799027705582592</v>
       </c>
-      <c r="N20" s="67">
+      <c r="N20">
         <v>-0.61890510255991305</v>
       </c>
-      <c r="O20" s="67">
+      <c r="O20">
         <v>1.8799027705582592</v>
       </c>
-      <c r="Q20" s="55" t="s">
+      <c r="Q20" s="52" t="s">
         <v>23</v>
       </c>
       <c r="R20" s="7" t="s">
@@ -8520,62 +8361,62 @@
         <v>8.0865157072275651E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G21" s="68" t="s">
+    <row r="21" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G21" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="H21" s="68">
+      <c r="H21" s="26">
         <v>7.2826122834573154E-2</v>
       </c>
-      <c r="I21" s="68">
+      <c r="I21" s="26">
         <v>0.31108188829558769</v>
       </c>
-      <c r="J21" s="68">
+      <c r="J21" s="26">
         <v>0.23410595593843866</v>
       </c>
-      <c r="K21" s="68">
+      <c r="K21" s="26">
         <v>0.82996954292996972</v>
       </c>
-      <c r="L21" s="68">
+      <c r="L21" s="26">
         <v>-0.91717528321239938</v>
       </c>
-      <c r="M21" s="68">
+      <c r="M21" s="26">
         <v>1.0628275288815456</v>
       </c>
-      <c r="N21" s="68">
+      <c r="N21" s="26">
         <v>-0.91717528321239938</v>
       </c>
-      <c r="O21" s="68">
+      <c r="O21" s="26">
         <v>1.0628275288815456</v>
       </c>
-      <c r="Q21" s="57" t="s">
+      <c r="Q21" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="R21" s="27" t="s">
+      <c r="R21" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="S21" s="49">
+      <c r="S21" s="47">
         <v>0.45939952066393192</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" s="23" t="s">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="21" t="s">
         <v>64</v>
       </c>
       <c r="G24" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>7.741099090035366</v>
       </c>
@@ -8589,7 +8430,7 @@
         <v>7.13966033596492</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>7.7454356102743809</v>
       </c>
@@ -8602,12 +8443,12 @@
       <c r="D26" s="8">
         <v>7.2011708832816783</v>
       </c>
-      <c r="G26" s="70" t="s">
+      <c r="G26" s="65" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="70"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="H26" s="65"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>7.8304256178203309</v>
       </c>
@@ -8620,14 +8461,14 @@
       <c r="D27" s="7">
         <v>6.9810057407217299</v>
       </c>
-      <c r="G27" s="67" t="s">
+      <c r="G27" t="s">
         <v>122</v>
       </c>
-      <c r="H27" s="67">
+      <c r="H27">
         <v>0.74397087646375004</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>7.7257714415879519</v>
       </c>
@@ -8640,14 +8481,14 @@
       <c r="D28" s="7">
         <v>6.8627579130514009</v>
       </c>
-      <c r="G28" s="67" t="s">
+      <c r="G28" t="s">
         <v>123</v>
       </c>
-      <c r="H28" s="67">
+      <c r="H28">
         <v>0.5534926650262405</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>7.7257714415879519</v>
       </c>
@@ -8660,14 +8501,14 @@
       <c r="D29" s="7">
         <v>6.7923444274708089</v>
       </c>
-      <c r="G29" s="67" t="s">
+      <c r="G29" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="67">
+      <c r="H29">
         <v>0.10698533005248094</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>7.6596429545646822</v>
       </c>
@@ -8680,140 +8521,138 @@
       <c r="D30" s="7">
         <v>6.6795991858443831</v>
       </c>
-      <c r="G30" s="67" t="s">
+      <c r="G30" t="s">
         <v>125</v>
       </c>
-      <c r="H30" s="67">
+      <c r="H30">
         <v>7.6882523495558103E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="24">
+    <row r="31" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22">
         <v>7.568379267836522</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="22">
         <v>8.2967958657700525</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="22">
         <v>5.8171111599632042</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="22">
         <v>6.7226297948554494</v>
       </c>
-      <c r="G31" s="68" t="s">
+      <c r="G31" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="H31" s="68">
+      <c r="H31" s="26">
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G33" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G34" s="69"/>
-      <c r="H34" s="69" t="s">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="G34" s="64"/>
+      <c r="H34" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="I34" s="69" t="s">
+      <c r="I34" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="J34" s="69" t="s">
+      <c r="J34" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="K34" s="69" t="s">
+      <c r="K34" s="64" t="s">
         <v>135</v>
       </c>
-      <c r="L34" s="69" t="s">
+      <c r="L34" s="64" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G35" s="67" t="s">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="G35" t="s">
         <v>128</v>
       </c>
-      <c r="H35" s="67">
+      <c r="H35">
         <v>3</v>
       </c>
-      <c r="I35" s="67">
+      <c r="I35">
         <v>2.1981624575145197E-2</v>
       </c>
-      <c r="J35" s="67">
+      <c r="J35">
         <v>7.3272081917150657E-3</v>
       </c>
-      <c r="K35" s="67">
+      <c r="K35">
         <v>1.2396048657493348</v>
       </c>
-      <c r="L35" s="67">
+      <c r="L35">
         <v>0.43202117516685606</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G36" s="67" t="s">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="G36" t="s">
         <v>129</v>
       </c>
-      <c r="H36" s="67">
+      <c r="H36">
         <v>3</v>
       </c>
-      <c r="I36" s="67">
+      <c r="I36">
         <v>1.7732767257135133E-2</v>
       </c>
-      <c r="J36" s="67">
+      <c r="J36">
         <v>5.9109224190450442E-3</v>
       </c>
-      <c r="K36" s="67"/>
-      <c r="L36" s="67"/>
-    </row>
-    <row r="37" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G37" s="68" t="s">
+    </row>
+    <row r="37" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G37" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="H37" s="68">
+      <c r="H37" s="26">
         <v>6</v>
       </c>
-      <c r="I37" s="68">
+      <c r="I37" s="26">
         <v>3.971439183228033E-2</v>
       </c>
-      <c r="J37" s="68"/>
-      <c r="K37" s="68"/>
-      <c r="L37" s="68"/>
-    </row>
-    <row r="38" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="Q38" s="71" t="s">
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+    </row>
+    <row r="38" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q38" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="R38" s="72"/>
-      <c r="S38" s="72"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G39" s="69"/>
-      <c r="H39" s="69" t="s">
+      <c r="R38" s="73"/>
+      <c r="S38" s="73"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="G39" s="64"/>
+      <c r="H39" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="I39" s="69" t="s">
+      <c r="I39" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="J39" s="69" t="s">
+      <c r="J39" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="K39" s="69" t="s">
+      <c r="K39" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="L39" s="69" t="s">
+      <c r="L39" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="M39" s="69" t="s">
+      <c r="M39" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="N39" s="69" t="s">
+      <c r="N39" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="O39" s="69" t="s">
+      <c r="O39" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="Q39" s="25" t="s">
+      <c r="Q39" s="23" t="s">
         <v>86</v>
       </c>
       <c r="R39" s="6" t="s">
@@ -8823,35 +8662,35 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G40" s="67" t="s">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="G40" t="s">
         <v>131</v>
       </c>
-      <c r="H40" s="67">
+      <c r="H40">
         <v>4.6027071697835797</v>
       </c>
-      <c r="I40" s="67">
+      <c r="I40">
         <v>1.6911952049598171</v>
       </c>
-      <c r="J40" s="67">
+      <c r="J40">
         <v>2.7215706124787293</v>
       </c>
-      <c r="K40" s="67">
+      <c r="K40">
         <v>7.2453368870255913E-2</v>
       </c>
-      <c r="L40" s="67">
+      <c r="L40">
         <v>-0.77943076175431525</v>
       </c>
-      <c r="M40" s="67">
+      <c r="M40">
         <v>9.9848451013214756</v>
       </c>
-      <c r="N40" s="67">
+      <c r="N40">
         <v>-0.77943076175431525</v>
       </c>
-      <c r="O40" s="67">
+      <c r="O40">
         <v>9.9848451013214756</v>
       </c>
-      <c r="Q40" s="23" t="s">
+      <c r="Q40" s="21" t="s">
         <v>17</v>
       </c>
       <c r="R40" s="7" t="s">
@@ -8861,35 +8700,35 @@
         <v>0.67580221289686704</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G41" s="67" t="s">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="G41" t="s">
         <v>48</v>
       </c>
-      <c r="H41" s="67">
+      <c r="H41">
         <v>0.67230105269544693</v>
       </c>
-      <c r="I41" s="67">
+      <c r="I41">
         <v>0.74080983335146799</v>
       </c>
-      <c r="J41" s="67">
+      <c r="J41">
         <v>0.90752177202335016</v>
       </c>
-      <c r="K41" s="67">
+      <c r="K41">
         <v>0.43103503632652562</v>
       </c>
-      <c r="L41" s="67">
+      <c r="L41">
         <v>-1.6852864643717724</v>
       </c>
-      <c r="M41" s="67">
+      <c r="M41">
         <v>3.0298885697626661</v>
       </c>
-      <c r="N41" s="67">
+      <c r="N41">
         <v>-1.6852864643717724</v>
       </c>
-      <c r="O41" s="67">
+      <c r="O41">
         <v>3.0298885697626661</v>
       </c>
-      <c r="Q41" s="23" t="s">
+      <c r="Q41" s="21" t="s">
         <v>17</v>
       </c>
       <c r="R41" s="7" t="s">
@@ -8899,91 +8738,91 @@
         <v>0.32419778655420278</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G42" s="67" t="s">
+    <row r="42" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G42" t="s">
         <v>50</v>
       </c>
-      <c r="H42" s="67">
+      <c r="H42">
         <v>0.10163173627153886</v>
       </c>
-      <c r="I42" s="67">
+      <c r="I42">
         <v>0.41582235887400953</v>
       </c>
-      <c r="J42" s="67">
+      <c r="J42">
         <v>0.24441142738630939</v>
       </c>
-      <c r="K42" s="67">
+      <c r="K42">
         <v>0.82267501442910396</v>
       </c>
-      <c r="L42" s="67">
+      <c r="L42">
         <v>-1.2217005933814093</v>
       </c>
-      <c r="M42" s="67">
+      <c r="M42">
         <v>1.4249640659244871</v>
       </c>
-      <c r="N42" s="67">
+      <c r="N42">
         <v>-1.2217005933814093</v>
       </c>
-      <c r="O42" s="67">
+      <c r="O42">
         <v>1.4249640659244871</v>
       </c>
-      <c r="Q42" s="26" t="s">
+      <c r="Q42" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="R42" s="27" t="s">
+      <c r="R42" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="S42" s="49">
+      <c r="S42" s="47">
         <v>5.4893011563366283E-10</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G43" s="68" t="s">
+    <row r="43" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G43" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="H43" s="68">
+      <c r="H43" s="26">
         <v>-0.46887136601784019</v>
       </c>
-      <c r="I43" s="68">
+      <c r="I43" s="26">
         <v>0.70655636190531124</v>
       </c>
-      <c r="J43" s="68">
+      <c r="J43" s="26">
         <v>-0.66360079860221499</v>
       </c>
-      <c r="K43" s="68">
+      <c r="K43" s="26">
         <v>0.55438599160298363</v>
       </c>
-      <c r="L43" s="68">
+      <c r="L43" s="26">
         <v>-2.717449049438097</v>
       </c>
-      <c r="M43" s="68">
+      <c r="M43" s="26">
         <v>1.7797063174024168</v>
       </c>
-      <c r="N43" s="68">
+      <c r="N43" s="26">
         <v>-2.717449049438097</v>
       </c>
-      <c r="O43" s="68">
+      <c r="O43" s="26">
         <v>1.7797063174024168</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="55" t="s">
+    <row r="46" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="A46" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="B46" s="55" t="s">
+      <c r="B46" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="C46" s="55" t="s">
+      <c r="C46" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="D46" s="55" t="s">
+      <c r="D46" s="52" t="s">
         <v>73</v>
       </c>
       <c r="G46" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>6.4150969591715956</v>
       </c>
@@ -8997,7 +8836,7 @@
         <v>7.0527210492323231</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="8">
         <v>6.7580945044277314</v>
       </c>
@@ -9010,12 +8849,12 @@
       <c r="D48" s="8">
         <v>7.1747243098363764</v>
       </c>
-      <c r="G48" s="70" t="s">
+      <c r="G48" s="65" t="s">
         <v>121</v>
       </c>
-      <c r="H48" s="70"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="H48" s="65"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
         <v>7.0175061429412562</v>
       </c>
@@ -9028,14 +8867,14 @@
       <c r="D49" s="7">
         <v>7.1974353540965907</v>
       </c>
-      <c r="G49" s="67" t="s">
+      <c r="G49" t="s">
         <v>122</v>
       </c>
-      <c r="H49" s="67">
+      <c r="H49">
         <v>0.994187651589854</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>6.9994224675079613</v>
       </c>
@@ -9048,14 +8887,14 @@
       <c r="D50" s="7">
         <v>7.1747243098363764</v>
       </c>
-      <c r="G50" s="67" t="s">
+      <c r="G50" t="s">
         <v>123</v>
       </c>
-      <c r="H50" s="67">
+      <c r="H50">
         <v>0.98840908657374904</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
         <v>7.0039741367226798</v>
       </c>
@@ -9068,14 +8907,14 @@
       <c r="D51" s="7">
         <v>7.2696167496081694</v>
       </c>
-      <c r="G51" s="67" t="s">
+      <c r="G51" t="s">
         <v>124</v>
       </c>
-      <c r="H51" s="67">
+      <c r="H51">
         <v>0.97681817314749819</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>7.0825485693552999</v>
       </c>
@@ -9088,168 +8927,166 @@
       <c r="D52" s="7">
         <v>7.2305631534092916</v>
       </c>
-      <c r="G52" s="67" t="s">
+      <c r="G52" t="s">
         <v>125</v>
       </c>
-      <c r="H52" s="67">
+      <c r="H52">
         <v>3.9370619891004696E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="24">
+    <row r="53" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="22">
         <v>7.1861443045223252</v>
       </c>
-      <c r="B53" s="24">
+      <c r="B53" s="22">
         <v>6.7867169506050811</v>
       </c>
-      <c r="C53" s="24">
+      <c r="C53" s="22">
         <v>7.4271441334086159</v>
       </c>
-      <c r="D53" s="24">
+      <c r="D53" s="22">
         <v>7.2591161280971006</v>
       </c>
-      <c r="G53" s="68" t="s">
+      <c r="G53" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="H53" s="68">
+      <c r="H53" s="26">
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G55" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G56" s="69"/>
-      <c r="H56" s="69" t="s">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="G56" s="64"/>
+      <c r="H56" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="I56" s="69" t="s">
+      <c r="I56" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="J56" s="69" t="s">
+      <c r="J56" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="K56" s="69" t="s">
+      <c r="K56" s="64" t="s">
         <v>135</v>
       </c>
-      <c r="L56" s="69" t="s">
+      <c r="L56" s="64" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G57" s="67" t="s">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="G57" t="s">
         <v>128</v>
       </c>
-      <c r="H57" s="67">
+      <c r="H57">
         <v>3</v>
       </c>
-      <c r="I57" s="67">
+      <c r="I57">
         <v>0.3965380143795606</v>
       </c>
-      <c r="J57" s="67">
+      <c r="J57">
         <v>0.13217933812652019</v>
       </c>
-      <c r="K57" s="67">
+      <c r="K57">
         <v>85.274477534721939</v>
       </c>
-      <c r="L57" s="67">
+      <c r="L57">
         <v>2.1111029119418373E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G58" s="67" t="s">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="G58" t="s">
         <v>129</v>
       </c>
-      <c r="H58" s="67">
+      <c r="H58">
         <v>3</v>
       </c>
-      <c r="I58" s="67">
+      <c r="I58">
         <v>4.6501371318059242E-3</v>
       </c>
-      <c r="J58" s="67">
+      <c r="J58">
         <v>1.5500457106019747E-3</v>
       </c>
-      <c r="K58" s="67"/>
-      <c r="L58" s="67"/>
-    </row>
-    <row r="59" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G59" s="68" t="s">
+    </row>
+    <row r="59" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G59" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="H59" s="68">
+      <c r="H59" s="26">
         <v>6</v>
       </c>
-      <c r="I59" s="68">
+      <c r="I59" s="26">
         <v>0.4011881515113665</v>
       </c>
-      <c r="J59" s="68"/>
-      <c r="K59" s="68"/>
-      <c r="L59" s="68"/>
-    </row>
-    <row r="60" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G61" s="69"/>
-      <c r="H61" s="69" t="s">
+      <c r="J59" s="26"/>
+      <c r="K59" s="26"/>
+      <c r="L59" s="26"/>
+    </row>
+    <row r="60" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="G61" s="64"/>
+      <c r="H61" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="I61" s="69" t="s">
+      <c r="I61" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="J61" s="69" t="s">
+      <c r="J61" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="K61" s="69" t="s">
+      <c r="K61" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="L61" s="69" t="s">
+      <c r="L61" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="M61" s="69" t="s">
+      <c r="M61" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="N61" s="69" t="s">
+      <c r="N61" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="O61" s="69" t="s">
+      <c r="O61" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="Q61" s="71" t="s">
+      <c r="Q61" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="R61" s="72"/>
-      <c r="S61" s="72"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G62" s="67" t="s">
+      <c r="R61" s="73"/>
+      <c r="S61" s="73"/>
+    </row>
+    <row r="62" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="G62" t="s">
         <v>131</v>
       </c>
-      <c r="H62" s="67">
+      <c r="H62">
         <v>-15.55333146150058</v>
       </c>
-      <c r="I62" s="67">
+      <c r="I62">
         <v>2.3111182145329354</v>
       </c>
-      <c r="J62" s="67">
+      <c r="J62">
         <v>-6.7297861977362441</v>
       </c>
-      <c r="K62" s="67">
+      <c r="K62">
         <v>6.6985339245472448E-3</v>
       </c>
-      <c r="L62" s="67">
+      <c r="L62">
         <v>-22.908341084414804</v>
       </c>
-      <c r="M62" s="67">
+      <c r="M62">
         <v>-8.1983218385863559</v>
       </c>
-      <c r="N62" s="67">
+      <c r="N62">
         <v>-22.908341084414804</v>
       </c>
-      <c r="O62" s="67">
+      <c r="O62">
         <v>-8.1983218385863559</v>
       </c>
-      <c r="Q62" s="56" t="s">
+      <c r="Q62" s="53" t="s">
         <v>86</v>
       </c>
       <c r="R62" s="6" t="s">
@@ -9259,35 +9096,35 @@
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="G63" s="67" t="s">
+    <row r="63" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="G63" t="s">
         <v>24</v>
       </c>
-      <c r="H63" s="67">
+      <c r="H63">
         <v>1.0712217158941915</v>
       </c>
-      <c r="I63" s="67">
+      <c r="I63">
         <v>0.24893188129409366</v>
       </c>
-      <c r="J63" s="67">
+      <c r="J63">
         <v>4.3032724869364012</v>
       </c>
-      <c r="K63" s="67">
+      <c r="K63">
         <v>2.309344466681278E-2</v>
       </c>
-      <c r="L63" s="67">
+      <c r="L63">
         <v>0.27900937000248027</v>
       </c>
-      <c r="M63" s="67">
+      <c r="M63">
         <v>1.8634340617859027</v>
       </c>
-      <c r="N63" s="67">
+      <c r="N63">
         <v>0.27900937000248027</v>
       </c>
-      <c r="O63" s="67">
+      <c r="O63">
         <v>1.8634340617859027</v>
       </c>
-      <c r="Q63" s="55" t="s">
+      <c r="Q63" s="52" t="s">
         <v>22</v>
       </c>
       <c r="R63" s="7" t="s">
@@ -9297,35 +9134,35 @@
         <v>0.31777391101652008</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="G64" s="67" t="s">
+    <row r="64" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="G64" t="s">
         <v>42</v>
       </c>
-      <c r="H64" s="67">
+      <c r="H64">
         <v>0.9050544989883258</v>
       </c>
-      <c r="I64" s="67">
+      <c r="I64">
         <v>0.98650421299138458</v>
       </c>
-      <c r="J64" s="67">
+      <c r="J64">
         <v>0.91743602010975889</v>
       </c>
-      <c r="K64" s="67">
+      <c r="K64">
         <v>0.42656962637205087</v>
       </c>
-      <c r="L64" s="67">
+      <c r="L64">
         <v>-2.2344421887929196</v>
       </c>
-      <c r="M64" s="67">
+      <c r="M64">
         <v>4.0445511867695707</v>
       </c>
-      <c r="N64" s="67">
+      <c r="N64">
         <v>-2.2344421887929196</v>
       </c>
-      <c r="O64" s="67">
+      <c r="O64">
         <v>4.0445511867695707</v>
       </c>
-      <c r="Q64" s="55" t="s">
+      <c r="Q64" s="52" t="s">
         <v>22</v>
       </c>
       <c r="R64" s="7" t="s">
@@ -9335,41 +9172,41 @@
         <v>0.68222606641491146</v>
       </c>
     </row>
-    <row r="65" spans="7:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G65" s="68" t="s">
+    <row r="65" spans="7:19" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G65" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="H65" s="68">
+      <c r="H65" s="26">
         <v>1.1981535190162029</v>
       </c>
-      <c r="I65" s="68">
+      <c r="I65" s="26">
         <v>0.70570865793492354</v>
       </c>
-      <c r="J65" s="68">
+      <c r="J65" s="26">
         <v>1.6978019265376363</v>
       </c>
-      <c r="K65" s="68">
+      <c r="K65" s="26">
         <v>0.18811035682836591</v>
       </c>
-      <c r="L65" s="68">
+      <c r="L65" s="26">
         <v>-1.0477263920355195</v>
       </c>
-      <c r="M65" s="68">
+      <c r="M65" s="26">
         <v>3.4440334300679254</v>
       </c>
-      <c r="N65" s="68">
+      <c r="N65" s="26">
         <v>-1.0477263920355195</v>
       </c>
-      <c r="O65" s="68">
+      <c r="O65" s="26">
         <v>3.4440334300679254</v>
       </c>
-      <c r="Q65" s="57" t="s">
+      <c r="Q65" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="R65" s="27" t="s">
+      <c r="R65" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="S65" s="49">
+      <c r="S65" s="47">
         <v>2.2568568492421111E-8</v>
       </c>
     </row>
